--- a/ACC-REM-001 — ADR-005 Accounting Architecture Remediation & Evidence Register.xlsx
+++ b/ACC-REM-001 — ADR-005 Accounting Architecture Remediation & Evidence Register.xlsx
@@ -19,597 +19,606 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="588">
   <si>
+    <t>ACC-REM-001 Dashboard</t>
+  </si>
+  <si>
+    <t>Status &amp; Acceptance Guide</t>
+  </si>
+  <si>
     <t>Evidence Checklist — Minimum Closure Pack</t>
   </si>
   <si>
-    <t>ACC-REM-001 Dashboard</t>
-  </si>
-  <si>
     <t>ACC-REM-001 — ADR-005 Accounting Architecture Remediation &amp; Evidence Register</t>
   </si>
   <si>
-    <t>Status &amp; Acceptance Guide</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>Total Issues</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Set By</t>
+  </si>
+  <si>
+    <t>Exit Criteria</t>
+  </si>
+  <si>
+    <t>Allowed Next State</t>
+  </si>
+  <si>
+    <t>Control Rule</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Issue confirmed and not yet started.</t>
+  </si>
+  <si>
+    <t>Purpose: controlled issue register for systematic remediation and independent evidence-based acceptance against ACC-REG-001 v1.0 and ADR-005 v1.0. Baseline repository: olamoooore/Ace-ERC.</t>
+  </si>
+  <si>
+    <t>Reviewer / Lead</t>
+  </si>
+  <si>
+    <t>Engineer accepts scope and begins implementation.</t>
+  </si>
+  <si>
+    <t>IN_PROGRESS / DEFERRED</t>
+  </si>
+  <si>
+    <t>Cannot be marked complete.</t>
+  </si>
+  <si>
+    <t>IN_PROGRESS</t>
+  </si>
+  <si>
+    <t>Engineer actively remediating.</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
     <t>Evidence Type</t>
   </si>
   <si>
-    <t>Purpose: controlled issue register for systematic remediation and independent evidence-based acceptance against ACC-REG-001 v1.0 and ADR-005 v1.0. Baseline repository: olamoooore/Ace-ERC.</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Interpretation</t>
-  </si>
-  <si>
-    <t>Total Issues</t>
+    <t>Required evidence pack complete.</t>
+  </si>
+  <si>
+    <t>EVIDENCE_SUBMITTED</t>
   </si>
   <si>
     <t>CONTROL NOTE: Observed / Affected Files are the minimum mandatory inspection scope, not a whitelist of files to patch. Engineer must complete dependency tracing across callers, models, migrations, APIs, jobs/listeners/events and tests before implementation. Any additional affected path must be recorded.</t>
   </si>
   <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>Set By</t>
-  </si>
-  <si>
-    <t>Exit Criteria</t>
-  </si>
-  <si>
-    <t>Allowed Next State</t>
-  </si>
-  <si>
-    <t>Control Rule</t>
-  </si>
-  <si>
-    <t>OPEN</t>
+    <t>Implementation claim alone is insufficient.</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Engineer has submitted complete repository evidence.</t>
+  </si>
+  <si>
+    <t>Submission Format</t>
+  </si>
+  <si>
+    <t>Independent review begins.</t>
+  </si>
+  <si>
+    <t>Acceptance Rule</t>
+  </si>
+  <si>
+    <t>HOSTILE_REVIEW</t>
+  </si>
+  <si>
+    <t>No self-acceptance.</t>
+  </si>
+  <si>
+    <t>Applies To</t>
   </si>
   <si>
     <t>Issue ID</t>
   </si>
   <si>
-    <t>Issue confirmed and not yet started.</t>
-  </si>
-  <si>
-    <t>Reviewer / Lead</t>
-  </si>
-  <si>
-    <t>Engineer accepts scope and begins implementation.</t>
-  </si>
-  <si>
-    <t>IN_PROGRESS / DEFERRED</t>
-  </si>
-  <si>
-    <t>Cannot be marked complete.</t>
+    <t>Reviewer Check</t>
+  </si>
+  <si>
+    <t>Independent code/test/evidence verification in progress.</t>
+  </si>
+  <si>
+    <t>Independent Reviewer</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>All acceptance criteria verified or a defect identified.</t>
+  </si>
+  <si>
+    <t>ACCEPTED / REJECTED</t>
   </si>
   <si>
     <t>Workstream</t>
   </si>
   <si>
+    <t>Commit / PR identity</t>
+  </si>
+  <si>
+    <t>Review against exact commit SHA.</t>
+  </si>
+  <si>
     <t>Capability</t>
   </si>
   <si>
-    <t>IN_PROGRESS</t>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
   </si>
   <si>
     <t>Severity</t>
   </si>
   <si>
-    <t>Mandatory</t>
-  </si>
-  <si>
-    <t>Engineer actively remediating.</t>
+    <t>Exact commit SHA and PR/branch used as claimed implementation baseline.</t>
+  </si>
+  <si>
+    <t>Evidence or implementation failed acceptance.</t>
   </si>
   <si>
     <t>Architecture Requirement</t>
   </si>
   <si>
-    <t>Engineer</t>
+    <t>SHA + PR link/number</t>
   </si>
   <si>
     <t>Issue Found</t>
   </si>
   <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Required evidence pack complete.</t>
+    <t>Must identify immutable code baseline.</t>
+  </si>
+  <si>
+    <t>Engineer reopens remediation against reviewer findings.</t>
+  </si>
+  <si>
+    <t>All issues</t>
   </si>
   <si>
     <t>Repository Evidence / Source</t>
   </si>
   <si>
-    <t>EVIDENCE_SUBMITTED</t>
+    <t>Reviewer findings must remain recorded.</t>
   </si>
   <si>
     <t>Observed / Affected Files</t>
   </si>
   <si>
-    <t>Submission Format</t>
-  </si>
-  <si>
-    <t>Implementation claim alone is insufficient.</t>
-  </si>
-  <si>
     <t>Minimum Dependency Trace</t>
   </si>
   <si>
-    <t>Acceptance Rule</t>
+    <t>ACCEPTED</t>
+  </si>
+  <si>
+    <t>Requirement independently verified against evidence.</t>
   </si>
   <si>
     <t>Dependency Trace Status</t>
   </si>
   <si>
-    <t>Applies To</t>
-  </si>
-  <si>
-    <t>Engineer has submitted complete repository evidence.</t>
-  </si>
-  <si>
     <t>Engineer Changed Files</t>
   </si>
   <si>
-    <t>Reviewer Check</t>
+    <t>Terminal unless later regression/change.</t>
+  </si>
+  <si>
+    <t>OPEN only via controlled regression/review</t>
   </si>
   <si>
     <t>Engineer Added / Changed Tests</t>
   </si>
   <si>
-    <t>Independent review begins.</t>
-  </si>
-  <si>
-    <t>Notes</t>
+    <t>No screenshot/AI claim can set ACCEPTED.</t>
   </si>
   <si>
     <t>Required Remediation</t>
   </si>
   <si>
-    <t>HOSTILE_REVIEW</t>
+    <t>DEFERRED</t>
   </si>
   <si>
     <t>Acceptance Evidence</t>
   </si>
   <si>
-    <t>No self-acceptance.</t>
+    <t>Explicitly postponed with approved reason and owner.</t>
   </si>
   <si>
     <t>Owner</t>
   </si>
   <si>
+    <t>Architecture Lead / Product Owner</t>
+  </si>
+  <si>
+    <t>Trigger/date/scope reached.</t>
+  </si>
+  <si>
+    <t>P0 cannot be deferred for ADR-005 implementation conformance/release acceptance without an explicit architecture decision.</t>
+  </si>
+  <si>
     <t>Target Commit / PR</t>
   </si>
   <si>
-    <t>Independent code/test/evidence verification in progress.</t>
-  </si>
-  <si>
     <t>Engineer Status</t>
   </si>
   <si>
-    <t>Independent Reviewer</t>
+    <t>DEPENDENCY TRACE STATUS</t>
   </si>
   <si>
     <t>Evidence Submitted</t>
   </si>
   <si>
-    <t>All acceptance criteria verified or a defect identified.</t>
-  </si>
-  <si>
     <t>Hostile Review</t>
   </si>
   <si>
-    <t>ACCEPTED / REJECTED</t>
-  </si>
-  <si>
     <t>Final Verdict</t>
   </si>
   <si>
-    <t>Review against exact commit SHA.</t>
-  </si>
-  <si>
     <t>Reviewer Notes</t>
   </si>
   <si>
     <t>Last Updated</t>
   </si>
   <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>Evidence or implementation failed acceptance.</t>
-  </si>
-  <si>
     <t>ACC-RM-001</t>
   </si>
   <si>
-    <t>Engineer reopens remediation against reviewer findings.</t>
-  </si>
-  <si>
-    <t>Commit / PR identity</t>
+    <t>Controlled remediation items in register</t>
   </si>
   <si>
     <t>Wave A — Accounting Authority</t>
   </si>
   <si>
-    <t>Reviewer findings must remain recorded.</t>
-  </si>
-  <si>
     <t>ACC-002</t>
   </si>
   <si>
+    <t>P0 Critical</t>
+  </si>
+  <si>
     <t>P0</t>
   </si>
   <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>ACCEPTED</t>
+    <t>NOT REVIEWED</t>
+  </si>
+  <si>
+    <t>NOT STARTED</t>
   </si>
   <si>
     <t>Operational domains submit business facts via DomainPostingRequest; Posting Policy Mapper derives authoritative accounting lines.</t>
   </si>
   <si>
-    <t>Exact commit SHA and PR/branch used as claimed implementation baseline.</t>
-  </si>
-  <si>
-    <t>Requirement independently verified against evidence.</t>
+    <t>Changed paths</t>
+  </si>
+  <si>
+    <t>Required caller/dependency discovery has not begun.</t>
   </si>
   <si>
     <t>Operational/domain services construct explicit DR/CR PostingRequestLine[] and therefore own journal recipes outside ACC-002.</t>
   </si>
   <si>
-    <t>SHA + PR link/number</t>
-  </si>
-  <si>
-    <t>Must identify immutable code baseline.</t>
-  </si>
-  <si>
-    <t>Terminal unless later regression/change.</t>
-  </si>
-  <si>
-    <t>All issues</t>
-  </si>
-  <si>
-    <t>OPEN only via controlled regression/review</t>
+    <t>Engineer / Reviewer</t>
+  </si>
+  <si>
+    <t>List every changed production/test/migration file relevant to the remediation.</t>
+  </si>
+  <si>
+    <t>Repository trace begins against exact branch/SHA.</t>
   </si>
   <si>
     <t>PostingRequest.php; PostingRequestLine.php; PostingEngine.php::validateRequest()/resolveLines(); AccountRoleResolver.php; key posting services across AR/AP/OCR/POS/Ecommerce/HRM/FX/Fixed Assets; related posting tests. Validation confirmed operational callers can construct DR/CR lines and supply accountId, with explicit accountId taking priority over central mapping. No DomainPostingRequest, PostingPolicyMapper, posting_profile_code or JournalPostingRequest was found. IntercompanyPostingService exists but no active caller was found.</t>
   </si>
   <si>
-    <t>No screenshot/AI claim can set ACCEPTED.</t>
-  </si>
-  <si>
-    <t>DEFERRED</t>
-  </si>
-  <si>
-    <t>Explicitly postponed with approved reason and owner.</t>
-  </si>
-  <si>
-    <t>Architecture Lead / Product Owner</t>
+    <t>Repository paths</t>
+  </si>
+  <si>
+    <t>Discovery only</t>
+  </si>
+  <si>
+    <t>No unexplained implementation path.</t>
+  </si>
+  <si>
+    <t>No implementation claim may rely on an untraced path.</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>Dependency/caller discovery is actively being performed.</t>
   </si>
   <si>
     <t>PostingRequest.php; PostingRequestLine.php; PostingEngine.php; AccountRoleResolver.php; InvoiceService.php; AccountingOriginBillService.php; AccountingOriginInvoiceService.php; BillPaymentService.php; VendorBillService.php; credit/debit-note services; BankReconciliationService.php; FxRevaluationService.php; DepreciationService.php; PaymentRefundService.php; OcrPostingService.php; PosPostingService.php; WebOrderPostingService.php; PayrollJournalService.php; ManualJournalPostingService.php; PaymentTransactionCompletionService.php; IntercompanyPostingService.php; JournalEntry/JournalEntryLine/JournalEntryLink; PostingAuditLog; related routes, migrations and tests.</t>
   </si>
   <si>
-    <t>Trigger/date/scope reached.</t>
-  </si>
-  <si>
-    <t>P0 cannot be deferred for ADR-005 implementation conformance/release acceptance without an explicit architecture decision.</t>
+    <t>All required dependency classes are classified.</t>
   </si>
   <si>
     <t>Trace every PostingRequest/PostingRequestLine caller; manual journals; posting profiles/config; account/tax/control mapping; APIs/controllers/routes; models/migrations/constraints; jobs/listeners/observers/events; permissions/RBAC; frontend triggers; tests; direct DB bypass paths; inactive/dead code and contradictory implementations. Prove whether operational callers can control DR/CR, accountId/accountMappingKey, tax account, journal and posting date, and whether explicit accountId overrides central mapping.</t>
   </si>
   <si>
-    <t>DEPENDENCY TRACE STATUS</t>
-  </si>
-  <si>
-    <t>NOT REVIEWED</t>
-  </si>
-  <si>
-    <t>Changed paths</t>
-  </si>
-  <si>
-    <t>List every changed production/test/migration file relevant to the remediation.</t>
-  </si>
-  <si>
-    <t>Repository paths</t>
-  </si>
-  <si>
-    <t>No unexplained implementation path.</t>
+    <t>Schema / migration</t>
+  </si>
+  <si>
+    <t>Discovery; narrow implementation only where trace already proves boundary</t>
+  </si>
+  <si>
+    <t>WHEN APPLICABLE</t>
+  </si>
+  <si>
+    <t>New callers found must be added to the inventory, not silently ignored.</t>
+  </si>
+  <si>
+    <t>Forward migration, backfill and compatibility/rollback strategy.</t>
   </si>
   <si>
     <t>PARTIAL</t>
   </si>
   <si>
-    <t>NOT STARTED</t>
+    <t>Migration path + SQL/schema diff</t>
+  </si>
+  <si>
+    <t>Defect may be validated, but required caller/dependency discovery remains materially incomplete.</t>
+  </si>
+  <si>
+    <t>No destructive/unscoped migration; existing data handled.</t>
+  </si>
+  <si>
+    <t>Reviewer / Engineer</t>
+  </si>
+  <si>
+    <t>Schema issues</t>
+  </si>
+  <si>
+    <t>Engineer completes missing trace and records final dispositions.</t>
+  </si>
+  <si>
+    <t>Implementation may begin only after the engineer closes the missing trace relevant to the changed path; EVIDENCE_SUBMITTED is prohibited while material trace remains partial.</t>
+  </si>
+  <si>
+    <t>API / DTO contract</t>
+  </si>
+  <si>
+    <t>An intern report is not required; engineer-owned discovery against the implementation SHA is authoritative evidence.</t>
+  </si>
+  <si>
+    <t>COMPLETE WITH UNRESOLVED EVIDENCE</t>
+  </si>
+  <si>
+    <t>New/changed command, event, DTO and reason-code contracts.</t>
+  </si>
+  <si>
+    <t>Must be independently ACCEPTED before ADR-005 implementation conformance/release acceptance</t>
+  </si>
+  <si>
+    <t>Contract + examples</t>
+  </si>
+  <si>
+    <t>Required dependency classes have been traced sufficiently to establish the defect/remediation boundary, but explicitly identified evidence remains unresolved.</t>
+  </si>
+  <si>
+    <t>Must match ADR authority boundary and remain deterministic.</t>
+  </si>
+  <si>
+    <t>P1 High</t>
+  </si>
+  <si>
+    <t>Contract issues</t>
+  </si>
+  <si>
+    <t>Unresolved items are either resolved by engineer discovery or explicitly proven non-blocking and carried into acceptance evidence.</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Required caller/dependency discovery has not begun.</t>
-  </si>
-  <si>
-    <t>Engineer / Reviewer</t>
-  </si>
-  <si>
-    <t>Schema / migration</t>
+    <t>Controlled implementation permitted; unresolved evidence remains mandatory before acceptance where material.</t>
   </si>
   <si>
     <t>Introduce governed DomainPostingRequest + versioned posting_profile_code + central Posting Policy Mapper. Restrict explicit line posting to authorised JournalPostingRequest/manual journal paths.</t>
   </si>
   <si>
-    <t>Repository trace begins against exact branch/SHA.</t>
+    <t>This state is not ACCEPTED and must not be used to hide an unknown implementation bypass.</t>
   </si>
   <si>
     <t>DTO/API contract; policy schema/versioning; migrated callers; positive posting tests; negative test proving operational caller cannot submit arbitrary GL lines; compatibility/migration evidence.</t>
   </si>
   <si>
-    <t>Discovery only</t>
-  </si>
-  <si>
-    <t>No implementation claim may rely on an untraced path.</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>Dependency/caller discovery is actively being performed.</t>
-  </si>
-  <si>
-    <t>All required dependency classes are classified.</t>
-  </si>
-  <si>
-    <t>Discovery; narrow implementation only where trace already proves boundary</t>
-  </si>
-  <si>
-    <t>New callers found must be added to the inventory, not silently ignored.</t>
-  </si>
-  <si>
-    <t>Defect may be validated, but required caller/dependency discovery remains materially incomplete.</t>
-  </si>
-  <si>
-    <t>Reviewer / Engineer</t>
-  </si>
-  <si>
-    <t>Controlled remediation items in register</t>
-  </si>
-  <si>
-    <t>Engineer completes missing trace and records final dispositions.</t>
-  </si>
-  <si>
-    <t>Implementation may begin only after the engineer closes the missing trace relevant to the changed path; EVIDENCE_SUBMITTED is prohibited while material trace remains partial.</t>
+    <t>Positive automated tests</t>
+  </si>
+  <si>
+    <t>COMPLETE</t>
+  </si>
+  <si>
+    <t>Required caller/dependency classes and contradictory implementations are classified for the claimed baseline.</t>
+  </si>
+  <si>
+    <t>Normal success path proving intended behavior.</t>
+  </si>
+  <si>
+    <t>Test file/method + execution output</t>
+  </si>
+  <si>
+    <t>Evidence pack references the completed inventory and exact SHA.</t>
+  </si>
+  <si>
+    <t>Executable; not screenshot-only.</t>
+  </si>
+  <si>
+    <t>Eligible for EVIDENCE_SUBMITTED after implementation evidence is complete.</t>
+  </si>
+  <si>
+    <t>Negative automated tests</t>
+  </si>
+  <si>
+    <t>Complete trace does not mean remediation is accepted.</t>
+  </si>
+  <si>
+    <t>Prohibited/invalid path must fail with expected canonical outcome/reason.</t>
+  </si>
+  <si>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>Trace cannot be completed because a required authority, environment, dependency or decision is unavailable.</t>
+  </si>
+  <si>
+    <t>High-priority conformance/hardening items</t>
+  </si>
+  <si>
+    <t>At least one meaningful prohibited path per issue.</t>
+  </si>
+  <si>
+    <t>Blocking dependency is resolved or explicit architecture decision is issued.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Implementation must not guess across the blocked authority.</t>
   </si>
   <si>
     <t>NO</t>
   </si>
   <si>
-    <t>P0 Critical</t>
-  </si>
-  <si>
-    <t>WHEN APPLICABLE</t>
-  </si>
-  <si>
-    <t>An intern report is not required; engineer-owned discovery against the implementation SHA is authoritative evidence.</t>
-  </si>
-  <si>
-    <t>Forward migration, backfill and compatibility/rollback strategy.</t>
-  </si>
-  <si>
-    <t>COMPLETE WITH UNRESOLVED EVIDENCE</t>
-  </si>
-  <si>
-    <t>Migration path + SQL/schema diff</t>
-  </si>
-  <si>
-    <t>No destructive/unscoped migration; existing data handled.</t>
-  </si>
-  <si>
-    <t>Required dependency classes have been traced sufficiently to establish the defect/remediation boundary, but explicitly identified evidence remains unresolved.</t>
-  </si>
-  <si>
-    <t>Schema issues</t>
-  </si>
-  <si>
-    <t>Unresolved items are either resolved by engineer discovery or explicitly proven non-blocking and carried into acceptance evidence.</t>
-  </si>
-  <si>
-    <t>API / DTO contract</t>
-  </si>
-  <si>
-    <t>Controlled implementation permitted; unresolved evidence remains mandatory before acceptance where material.</t>
-  </si>
-  <si>
-    <t>New/changed command, event, DTO and reason-code contracts.</t>
-  </si>
-  <si>
-    <t>This state is not ACCEPTED and must not be used to hide an unknown implementation bypass.</t>
-  </si>
-  <si>
-    <t>Contract + examples</t>
-  </si>
-  <si>
-    <t>Must match ADR authority boundary and remain deterministic.</t>
-  </si>
-  <si>
-    <t>COMPLETE</t>
-  </si>
-  <si>
-    <t>Contract issues</t>
-  </si>
-  <si>
-    <t>Required caller/dependency classes and contradictory implementations are classified for the claimed baseline.</t>
-  </si>
-  <si>
-    <t>Positive automated tests</t>
-  </si>
-  <si>
-    <t>Evidence pack references the completed inventory and exact SHA.</t>
-  </si>
-  <si>
-    <t>Normal success path proving intended behavior.</t>
-  </si>
-  <si>
-    <t>Eligible for EVIDENCE_SUBMITTED after implementation evidence is complete.</t>
-  </si>
-  <si>
-    <t>Test file/method + execution output</t>
-  </si>
-  <si>
-    <t>Executable; not screenshot-only.</t>
-  </si>
-  <si>
-    <t>Complete trace does not mean remediation is accepted.</t>
+    <t>P0 block requires escalation; absence of evidence is not permission to implement assumptions.</t>
+  </si>
+  <si>
+    <t>Concurrency / idempotency</t>
+  </si>
+  <si>
+    <t>ENGINEER DISCOVERY RULE</t>
+  </si>
+  <si>
+    <t>Race, retry and duplicate-command behavior.</t>
+  </si>
+  <si>
+    <t>The engineer is responsible for repository discovery/caller inventory on the exact implementation baseline even when prior reviewer or intern traces exist.</t>
+  </si>
+  <si>
+    <t>Automated test + DB/result evidence</t>
+  </si>
+  <si>
+    <t>Final evidence pack contains immutable SHA, caller/reference inventory and remaining exceptions.</t>
+  </si>
+  <si>
+    <t>No duplicate authoritative effect.</t>
+  </si>
+  <si>
+    <t>Posting, reversal, close, payment, events</t>
+  </si>
+  <si>
+    <t>Mandatory for every remediation item</t>
+  </si>
+  <si>
+    <t>Prior reports accelerate discovery but never replace engineer accountability or independent hostile acceptance.</t>
+  </si>
+  <si>
+    <t>Failure injection / atomicity</t>
+  </si>
+  <si>
+    <t>Force failure between authoritative writes and verify all-or-nothing or designed recovery.</t>
+  </si>
+  <si>
+    <t>Automated test + before/after DB state</t>
+  </si>
+  <si>
+    <t>No partial authoritative state.</t>
   </si>
   <si>
     <t>NOT ACCEPTED</t>
   </si>
   <si>
-    <t>BLOCKED</t>
-  </si>
-  <si>
-    <t>Negative automated tests</t>
-  </si>
-  <si>
-    <t>Trace cannot be completed because a required authority, environment, dependency or decision is unavailable.</t>
+    <t>Posting, reversal, close, outbox</t>
   </si>
   <si>
     <t>Intern Repository Gap Analysis V2 was rejected for evidence completion, but an intern V2.1 is NOT an implementation prerequisite. Core ACC-RM-001 finding remains VALIDATED. Engineer may independently complete the required caller/dependency discovery against the exact implementation branch/SHA before coding and must include the final caller inventory in the evidence pack. Dependency Trace remains PARTIAL until that engineer trace closes: complete PostingRequest/PostingRequestLine caller inventory including PaymentRefundService fallback; distinguish raw GL authority from business-reference-to-GL translation outside ACC-002; analyse fallback accounting-policy divergence; cross-link authorization to ACC-RM-019.</t>
   </si>
   <si>
-    <t>Prohibited/invalid path must fail with expected canonical outcome/reason.</t>
-  </si>
-  <si>
-    <t>Blocking dependency is resolved or explicit architecture decision is issued.</t>
-  </si>
-  <si>
-    <t>At least one meaningful prohibited path per issue.</t>
-  </si>
-  <si>
-    <t>Implementation must not guess across the blocked authority.</t>
-  </si>
-  <si>
-    <t>P0 block requires escalation; absence of evidence is not permission to implement assumptions.</t>
-  </si>
-  <si>
-    <t>ENGINEER DISCOVERY RULE</t>
-  </si>
-  <si>
-    <t>Concurrency / idempotency</t>
-  </si>
-  <si>
-    <t>The engineer is responsible for repository discovery/caller inventory on the exact implementation baseline even when prior reviewer or intern traces exist.</t>
-  </si>
-  <si>
-    <t>Race, retry and duplicate-command behavior.</t>
-  </si>
-  <si>
-    <t>Must be independently ACCEPTED before ADR-005 implementation conformance/release acceptance</t>
-  </si>
-  <si>
-    <t>Final evidence pack contains immutable SHA, caller/reference inventory and remaining exceptions.</t>
-  </si>
-  <si>
-    <t>Automated test + DB/result evidence</t>
-  </si>
-  <si>
-    <t>Mandatory for every remediation item</t>
-  </si>
-  <si>
-    <t>No duplicate authoritative effect.</t>
-  </si>
-  <si>
-    <t>P1 High</t>
+    <t>Not yet started</t>
+  </si>
+  <si>
+    <t>Runtime trace</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Representative request/workflow trace including IDs, reason codes and resulting authoritative records.</t>
+  </si>
+  <si>
+    <t>Sanitised request/response + trace IDs</t>
+  </si>
+  <si>
+    <t>Must be reproducible from claimed baseline.</t>
   </si>
   <si>
     <t>ACC-RM-002</t>
   </si>
   <si>
-    <t>Prior reports accelerate discovery but never replace engineer accountability or independent hostile acceptance.</t>
-  </si>
-  <si>
-    <t>Posting, reversal, close, payment, events</t>
-  </si>
-  <si>
-    <t>Failure injection / atomicity</t>
+    <t>Audit / event evidence</t>
   </si>
   <si>
     <t>Reversal Engine supports FULL_REVERSAL, PARTIAL_REVERSAL, CORRECT_AND_REPOST and component-aware reversal basis/lineage.</t>
   </si>
   <si>
-    <t>Force failure between authoritative writes and verify all-or-nothing or designed recovery.</t>
-  </si>
-  <si>
     <t>Current reversal is a full mirror reversal by swapping debit/credit across all original lines; component-aware partial reversal contract is not implemented.</t>
   </si>
   <si>
-    <t>Automated test + before/after DB state</t>
-  </si>
-  <si>
-    <t>No partial authoritative state.</t>
-  </si>
-  <si>
-    <t>Posting, reversal, close, outbox</t>
+    <t>Audit transition and required authoritative event/outbox evidence.</t>
+  </si>
+  <si>
+    <t>DB/event IDs + publisher evidence</t>
   </si>
   <si>
     <t>backend/app/Accounting/DTOs/ReversalRequest.php; backend/app/Accounting/PostingEngine.php::reverse(); DocumentCorrectionService.php; PaymentCorrectionService.php; InvoiceController.php::reverseJournalEntry(); PaymentRefundService.php; WebOrderPostingService.php; PayrollJournalService.php; OcrPostingService.php; PosPostingService.php; DocumentCorrectionPolicyService.php; correction models/migrations/tests. Review confirmed PostingEngine performs full mirror reversal only. No reversal_mode, reversal components or remaining reversible amount found. PaymentRefundService can track partial refund amounts but the GL reversal still reverses the full original journal. Active invoice reset-to-draft also creates reversal directly outside PostingEngine.</t>
   </si>
   <si>
-    <t>Runtime trace</t>
+    <t>One authoritative publisher; retry/idempotency proven.</t>
   </si>
   <si>
     <t>ReversalRequest.php; PostingEngine.php; JournalEntry.php; JournalEntryLink.php; PostingAuditLog.php; Payment.php; BillPayment.php; InvoiceController.php; JournalEntriesController.php; DocumentCorrectionsController.php; PaymentCorrectionsController.php; DocumentCorrectionService.php; PaymentCorrectionService.php; PaymentRefundService.php; AccountingAccessService.php; PaymentController.php; WebOrderPostingService.php; PosPostingService.php; PosSyncService.php; OcrPostingService.php; PayrollJournalService.php; correction/refund/journal-link migrations; PaymentRefundServiceTest.php; AFM001AccountingFailureModelTest.php; AuditFixesTest.php; WS06ChannelRuntimeConvergenceTest.php.</t>
   </si>
   <si>
-    <t>Representative request/workflow trace including IDs, reason codes and resulting authoritative records.</t>
-  </si>
-  <si>
-    <t>Sanitised request/response + trace IDs</t>
-  </si>
-  <si>
-    <t>Must be reproducible from claimed baseline.</t>
+    <t>Posting, reversal, close, finding, payment</t>
   </si>
   <si>
     <t>Trace every reversal entry point and direct journal reversal path; full/partial/correct-and-repost behaviour; payment refund amount flow and remaining refundable state; invoice/bill/journal corrections; customer and bill-payment corrections; credit/debit-note correction paths; POS/Offline POS; Ecommerce; OCR; Payroll; manual journals; controllers/routes; permissions/RBAC; models/migrations/constraints; lineage/idempotency controls; tests; inactive/dead code; and contradictory reversal implementations. Prove whether requested partial amounts/components reach the reversal engine and identify any path bypassing PostingEngine::reverse().</t>
   </si>
   <si>
-    <t>Audit / event evidence</t>
-  </si>
-  <si>
-    <t>Audit transition and required authoritative event/outbox evidence.</t>
-  </si>
-  <si>
-    <t>DB/event IDs + publisher evidence</t>
-  </si>
-  <si>
-    <t>High-priority conformance/hardening items</t>
+    <t>Engineer actively remediating</t>
   </si>
   <si>
     <t>Implement reversal_mode, reversal_basis, reversal_components[], deterministic policy-derived components and component_remaining_reversible_amount.</t>
   </si>
   <si>
-    <t>One authoritative publisher; retry/idempotency proven.</t>
+    <t>Caller / dependency inventory</t>
   </si>
   <si>
     <t>Schema/DTO; component lineage persistence; full/partial/correct-and-repost tests; over-reversal negative tests; balanced-entry proof.</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Posting, reversal, close, finding, payment</t>
-  </si>
-  <si>
-    <t>Caller / dependency inventory</t>
-  </si>
-  <si>
     <t>Engineer-owned repository discovery against exact implementation SHA; all authoritative callers, alternate mutation paths, bypasses, jobs/listeners/imports/integrations and dead/inactive paths classified.</t>
   </si>
   <si>
@@ -619,34 +628,43 @@
     <t>No unexplained caller or bypass remains for the changed authority.</t>
   </si>
   <si>
+    <t>Intern Repository Gap Analysis V2 was rejected for evidence completion, but an intern V2.1 is NOT an implementation prerequisite. Core ACC-RM-002 finding remains VALIDATED. Engineer may independently complete reversal caller/dependency discovery against the exact implementation branch/SHA before coding and must include the final inventory in the evidence pack. Dependency Trace remains PARTIAL until closed: exact PaymentRefund branches; PaymentCorrection stale reverse signature; BillPayment-to-Payment type incompatibility; multi-payment settlement defect cross-linked ACC-RM-013; POS fail-open GL divergence cross-linked ACC-RM-003; authorization cross-linked ACC-RM-019.</t>
+  </si>
+  <si>
     <t>All issues; mandatory before EVIDENCE_SUBMITTED</t>
   </si>
   <si>
-    <t>Intern Repository Gap Analysis V2 was rejected for evidence completion, but an intern V2.1 is NOT an implementation prerequisite. Core ACC-RM-002 finding remains VALIDATED. Engineer may independently complete reversal caller/dependency discovery against the exact implementation branch/SHA before coding and must include the final inventory in the evidence pack. Dependency Trace remains PARTIAL until closed: exact PaymentRefund branches; PaymentCorrection stale reverse signature; BillPayment-to-Payment type incompatibility; multi-payment settlement defect cross-linked ACC-RM-013; POS fail-open GL divergence cross-linked ACC-RM-003; authorization cross-linked ACC-RM-019.</t>
-  </si>
-  <si>
     <t>ACC-RM-003</t>
   </si>
   <si>
     <t>Prior reviewer/intern traces are inputs only; engineer owns the final inventory.</t>
   </si>
   <si>
+    <t>Reversal posting, authoritative ReversalRelationship, component consumption, transition evidence and required outbox record commit or roll back together.</t>
+  </si>
+  <si>
     <t>Capacity / concurrency control</t>
   </si>
   <si>
-    <t>Reversal posting, authoritative ReversalRelationship, component consumption, transition evidence and required outbox record commit or roll back together.</t>
+    <t>PROVEN P0. PostingEngine::reverse() is atomic only for reversal journal/lines/JournalEntryLink/PostingAuditLog. DocumentCorrectionService mutates document lifecycle and creates DocumentCorrectionLink after that transaction returns; those writes can fail independently after GL reversal. POS/offline refund paths also contain caught GL failures that can allow operational refund state to continue. No first-class ReversalRelationship/component-consumption/outbox authority is demonstrated.</t>
+  </si>
+  <si>
+    <t>PostingEngine.php::reverse(); DocumentCorrectionService.php; DocumentCorrectionLink model/migrations; PaymentCorrectionService.php; PaymentRefundService.php; PosSyncService.php; WebOrderPostingService.php positive outer-transaction pattern; JournalEntryLink.php; PostingAuditLog.php; reversal/correction tests.</t>
   </si>
   <si>
     <t>Execution-time lock/reload/version/invariant revalidation for commands consuming balance, quantity, reversible amount, match capacity or lifecycle eligibility.</t>
   </si>
   <si>
+    <t>PostingEngine.php; JournalEntry.php; JournalEntryLink.php; PostingAuditLog.php; ReversalRequest.php; DocumentCorrectionService.php; DocumentLifecycleService.php; DocumentVersionLinkService.php; DocumentCorrectionLink.php; DocumentCorrectionsController.php; PaymentCorrectionService.php; PaymentRefundService.php; PaymentCorrectionsController.php; InvoiceController.php; WebOrderPostingService.php; OcrPostingService.php; PosPostingService.php; PosOrderController.php; PosSyncService.php; PayrollJournalService.php; JournalEntryObserver.php; EventManagement outbox code; related correction migrations and reversal/atomicity tests.</t>
+  </si>
+  <si>
     <t>Concurrent automated tests + before/after DB state</t>
   </si>
   <si>
-    <t>Not yet started</t>
-  </si>
-  <si>
-    <t>PROVEN P0. PostingEngine::reverse() is atomic only for reversal journal/lines/JournalEntryLink/PostingAuditLog. DocumentCorrectionService mutates document lifecycle and creates DocumentCorrectionLink after that transaction returns; those writes can fail independently after GL reversal. POS/offline refund paths also contain caught GL failures that can allow operational refund state to continue. No first-class ReversalRelationship/component-consumption/outbox authority is demonstrated.</t>
+    <t>Awaiting hostile review</t>
+  </si>
+  <si>
+    <t>Trace reversal transaction end-to-end including journal/ledger/link/audit/event, retry/idempotency, migrations/constraints and failure handling. Prove no authoritative reversal artifact commits alone.</t>
   </si>
   <si>
     <t>Exactly one valid effect; competing stale command returns canonical CONFLICT/BLOCKED outcome.</t>
@@ -655,24 +673,21 @@
     <t>ACC-RM-016 and related payment/reversal/close/reconciliation commands</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>PostingEngine.php::reverse(); DocumentCorrectionService.php; DocumentCorrectionLink model/migrations; PaymentCorrectionService.php; PaymentRefundService.php; PosSyncService.php; WebOrderPostingService.php positive outer-transaction pattern; JournalEntryLink.php; PostingAuditLog.php; reversal/correction tests.</t>
-  </si>
-  <si>
-    <t>PostingEngine.php; JournalEntry.php; JournalEntryLink.php; PostingAuditLog.php; ReversalRequest.php; DocumentCorrectionService.php; DocumentLifecycleService.php; DocumentVersionLinkService.php; DocumentCorrectionLink.php; DocumentCorrectionsController.php; PaymentCorrectionService.php; PaymentRefundService.php; PaymentCorrectionsController.php; InvoiceController.php; WebOrderPostingService.php; OcrPostingService.php; PosPostingService.php; PosOrderController.php; PosSyncService.php; PayrollJournalService.php; JournalEntryObserver.php; EventManagement outbox code; related correction migrations and reversal/atomicity tests.</t>
+    <t>Accepted</t>
   </si>
   <si>
     <t>Include positive regression for existing correct locking controls.</t>
   </si>
   <si>
-    <t>Trace reversal transaction end-to-end including journal/ledger/link/audit/event, retry/idempotency, migrations/constraints and failure handling. Prove no authoritative reversal artifact commits alone.</t>
+    <t>Create one authoritative reversal command transaction that includes reversal journal/lines, ReversalRelationship, component consumption, document/payment lifecycle mutation, correction lineage, audit and required outbox record. Caller-specific side effects must either join the same transaction or use an explicit recoverable saga/state machine. Remove fail-open accounting divergence.</t>
   </si>
   <si>
     <t>Source confirmation / promotion idempotency</t>
   </si>
   <si>
+    <t>Failure injection after GL reversal, lifecycle mutation, lineage write, audit and outbox; all-or-nothing proof; POS/offline GL failure cannot return operational success; idempotent retry; no orphan reversal/document state; regression for WebOrder outer-transaction pattern.</t>
+  </si>
+  <si>
     <t>Human-confirmed reviewed source version, atomic source claim, unique source-to-canonical destination and replay-safe canonical result.</t>
   </si>
   <si>
@@ -682,60 +697,84 @@
     <t>No self-promotion, no duplicate canonical document, edit-after-review forces reconfirmation.</t>
   </si>
   <si>
-    <t>Create one authoritative reversal command transaction that includes reversal journal/lines, ReversalRelationship, component consumption, document/payment lifecycle mutation, correction lineage, audit and required outbox record. Caller-specific side effects must either join the same transaction or use an explicit recoverable saga/state machine. Remove fail-open accounting divergence.</t>
-  </si>
-  <si>
     <t>ACC-RM-017; OCR/source-derived creation</t>
   </si>
   <si>
-    <t>Failure injection after GL reversal, lifecycle mutation, lineage write, audit and outbox; all-or-nothing proof; POS/offline GL failure cannot return operational success; idempotent retry; no orphan reversal/document state; regression for WebOrder outer-transaction pattern.</t>
+    <t>VALIDATED P0 at immutable trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. Central journal reversal atomicity is a positive control but does not cover document/payment lineage. Engineer must complete final caller inventory against implementation SHA before EVIDENCE_SUBMITTED. Cross-link ACC-RM-002, 012, 013 and 016.</t>
   </si>
   <si>
     <t>NEEDS_REVIEW or AI confidence never grants promotion authority.</t>
   </si>
   <si>
+    <t>ACC-RM-004</t>
+  </si>
+  <si>
     <t>Import staging / commit evidence</t>
   </si>
   <si>
+    <t>Wave C — Platform Hardening</t>
+  </si>
+  <si>
+    <t>ACC-001</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
     <t>Durable file/batch/row staging, validation/mapping/review/preview state and explicit idempotent commit through canonical domain commands.</t>
   </si>
   <si>
+    <t>Independently accepted</t>
+  </si>
+  <si>
+    <t>Accounting-period authority must support legal-entity/accounting-book context where applicable.</t>
+  </si>
+  <si>
     <t>Batch/row records + preview/commit tests + restart/retry evidence</t>
   </si>
   <si>
+    <t>VALIDATED. FiscalPeriod authority is tenant-schema scoped but does not carry demonstrated legal_entity_id/entity_book_id while posting and close commands already carry entity/book context. Tenant isolation itself is not the defect; the unresolved design question is the canonical period scope policy and migration/backfill strategy.</t>
+  </si>
+  <si>
     <t>Before commit, authoritative live mutations are zero; partial failure is truthful/recoverable.</t>
   </si>
   <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>FiscalPeriod model/migration; FiscalPeriodsController.php; FiscalPeriodValidator.php; PostingRequest.php; PostingEngine.php; FinancialCloseCycleService.php; CloseCycle.php; entity/book models; MultiEntityIntegrationTest.php.</t>
+  </si>
+  <si>
     <t>ACC-RM-018 and domain imports</t>
   </si>
   <si>
-    <t>Engineer actively remediating</t>
+    <t>FiscalPeriod.php; fiscal_periods migration; FiscalPeriodsController.php; FiscalPeriodValidator.php; PostingRequest.php; PostingEngine.php; ManualJournalPostingService.php; OcrPostingService.php; FinancialCloseCycleService.php; CloseCycle.php; Financial Close cycle migrations; LockDate.php; lock-date migrations; company_settings lock-date migration; EnsureAccountingLockManageAccess.php; AccountingAccessService.php; CloseCyclesPage.tsx; closeApi.ts; FiscalPeriodTest.php; MultiEntityIntegrationTest.php; related fiscal-period test documentation.</t>
   </si>
   <si>
     <t>Reuse shared staging authority; no domain-local parallel import engine.</t>
   </si>
   <si>
+    <t>Trace period creation/lookup/current selection/close/reopen/lock/posting validation/reporting by tenant/entity/book. Confirm approved scoping policy before schema change.</t>
+  </si>
+  <si>
     <t>Approval / SoD / stale-decision evidence</t>
   </si>
   <si>
-    <t>VALIDATED P0 at immutable trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. Central journal reversal atomicity is a positive control but does not cover document/payment lineage. Engineer must complete final caller inventory against implementation SHA before EVIDENCE_SUBMITTED. Cross-link ACC-RM-002, 012, 013 and 016.</t>
-  </si>
-  <si>
     <t>Authoritative approval decision, approver eligibility/quorum/SoD, document/version binding and execution-time permission revalidation.</t>
   </si>
   <si>
+    <t>Approve one canonical FiscalPeriod scope policy, then migrate schema/lookups/close/posting validation accordingly. Preserve tenant isolation and do not add entity/book fields merely to duplicate an already-authoritative relationship if architecture proves another deterministic scope.</t>
+  </si>
+  <si>
     <t>Decision records + RBAC matrix + negative tests</t>
   </si>
   <si>
-    <t>ACC-RM-004</t>
+    <t>Migration/backfill or deterministic relationship proof; period creation/current lookup/post/close/reopen by entity/book; duplicate-period isolation; cross-entity/book negative tests; legacy compatibility.</t>
   </si>
   <si>
     <t>Write permission alone cannot post/close/reverse; self-approval and stale approval fail.</t>
   </si>
   <si>
-    <t>Wave C — Platform Hardening</t>
-  </si>
-  <si>
     <t>ACC-RM-014, ACC-RM-019 and related close/posting commands</t>
   </si>
   <si>
@@ -745,43 +784,52 @@
     <t>Reconciliation source / match lifecycle</t>
   </si>
   <si>
+    <t>Returned for remediation</t>
+  </si>
+  <si>
+    <t>VALIDATED scope defect; tenant isolation itself is not proven defective. Engineer must confirm the approved entity/book period model and migration impact against implementation SHA before changing schema.</t>
+  </si>
+  <si>
     <t>Durable statement/source identity, one match lifecycle, account/date authority, human confirmation, completion/reopen lineage and concurrency-safe amount conservation.</t>
   </si>
   <si>
+    <t>Acceptance %</t>
+  </si>
+  <si>
+    <t>ACC-RM-005</t>
+  </si>
+  <si>
     <t>Statement→match→GL→journal→source evidence + concurrency tests</t>
   </si>
   <si>
+    <t>ACC-001 / ACC-011</t>
+  </si>
+  <si>
     <t>No split-brain reconciled state; completed reconciliation immutable except governed reopen/supersede.</t>
   </si>
   <si>
     <t>ACC-RM-020</t>
   </si>
   <si>
-    <t>ACC-001</t>
-  </si>
-  <si>
-    <t>Awaiting hostile review</t>
-  </si>
-  <si>
-    <t>P1</t>
+    <t>Period/transaction locks must be scoped to the applicable accounting authority context.</t>
+  </si>
+  <si>
+    <t>PROVEN. LockDate has no demonstrated legal-entity/book scope and lock selection is not entity/book-aware. A separate LockDateOverride request/approval workflow exists, but PostingEngine does not demonstrate consumption of that approved record as execution authority; it instead accepts overrideReason/approvedBy and writes its own override evidence. Frontend exposes override request/history without a corresponding approval action.</t>
   </si>
   <si>
     <t>Preserve proven unique GL-line and matching controls.</t>
   </si>
   <si>
-    <t>Accepted</t>
-  </si>
-  <si>
-    <t>Accounting-period authority must support legal-entity/accounting-book context where applicable.</t>
+    <t>LockDate.php and migrations; lock validation/override services/controllers; PostingEngine override validation/logging; FinancialCloseCycleService.php; lockDatesApi.ts; Shared RBAC/approval services; override tests.</t>
   </si>
   <si>
     <t>Event / outbox runtime evidence</t>
   </si>
   <si>
-    <t>VALIDATED. FiscalPeriod authority is tenant-schema scoped but does not carry demonstrated legal_entity_id/entity_book_id while posting and close commands already carry entity/book context. Tenant isolation itself is not the defect; the unresolved design question is the canonical period scope policy and migration/backfill strategy.</t>
-  </si>
-  <si>
-    <t>FiscalPeriod model/migration; FiscalPeriodsController.php; FiscalPeriodValidator.php; PostingRequest.php; PostingEngine.php; FinancialCloseCycleService.php; CloseCycle.php; entity/book models; MultiEntityIntegrationTest.php.</t>
+    <t>tenant lock-date migration; LockDate.php; lock validation/override services; FinancialCloseCycleService.php; posting validators consuming lock state.</t>
+  </si>
+  <si>
+    <t>Trace all lock types/setters/overrides/reopen/posting validation and entity/book context. Identify intentionally tenant-wide locks and permission/SoD for override.</t>
   </si>
   <si>
     <t>Originating transaction and required event record are atomic; processor is registered/runnable; consumer success equals a verified real side effect; retry/idempotency/dead-letter work.</t>
@@ -790,99 +838,51 @@
     <t>Outbox/event IDs + processor execution + failure-injection tests</t>
   </si>
   <si>
-    <t>FiscalPeriod.php; fiscal_periods migration; FiscalPeriodsController.php; FiscalPeriodValidator.php; PostingRequest.php; PostingEngine.php; ManualJournalPostingService.php; OcrPostingService.php; FinancialCloseCycleService.php; CloseCycle.php; Financial Close cycle migrations; LockDate.php; lock-date migrations; company_settings lock-date migration; EnsureAccountingLockManageAccess.php; AccountingAccessService.php; CloseCyclesPage.tsx; closeApi.ts; FiscalPeriodTest.php; MultiEntityIntegrationTest.php; related fiscal-period test documentation.</t>
-  </si>
-  <si>
     <t>No commit→dispatch loss window, false-success consumer or duplicate authoritative event mechanism.</t>
   </si>
   <si>
-    <t>Trace period creation/lookup/current selection/close/reopen/lock/posting validation/reporting by tenant/entity/book. Confirm approved scoping policy before schema change.</t>
-  </si>
-  <si>
     <t>ACC-RM-012 and ACC-RM-021</t>
   </si>
   <si>
+    <t>Define canonical lock scope and one override authority. Entity/book-aware lock evaluation must consume the approved override decision/reference at execution time; PostingEngine must not infer approval from caller-supplied IDs. Align close/reopen and frontend approval workflow; retain explicit tenant-wide locks only where policy defines them.</t>
+  </si>
+  <si>
+    <t>Entity/book lock isolation; approved override required and consumed by ID/version; unapproved/stale/self-approved override blocked; frontend request→approval→retry flow; close/reopen consistency; audit/SoD evidence.</t>
+  </si>
+  <si>
     <t>Reuse/converge existing event/outbox assets; do not build a third mechanism.</t>
   </si>
   <si>
     <t>Evidence drill-down / UI authority</t>
   </si>
   <si>
-    <t>Approve one canonical FiscalPeriod scope policy, then migrate schema/lookups/close/posting validation accordingly. Preserve tenant isolation and do not add entity/book fields merely to duplicate an already-authoritative relationship if architecture proves another deterministic scope.</t>
-  </si>
-  <si>
-    <t>Migration/backfill or deterministic relationship proof; period creation/current lookup/post/close/reopen by entity/book; duplicate-period isolation; cross-entity/book negative tests; legacy compatibility.</t>
-  </si>
-  <si>
     <t>Permission-safe UI proves canonical source/destination/authority references and renders backend eligibility/reason codes without creating a second business authority.</t>
   </si>
   <si>
     <t>Browser/API trace + source IDs + negative permission tests</t>
   </si>
   <si>
-    <t>Independently accepted</t>
+    <t>VALIDATED at trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. Two override representations currently exist; do not create a third. Cross-link ACC-RM-014/019 and ACC-UI-RM-002.</t>
   </si>
   <si>
     <t>UI discoverability and drill-down reach the existing canonical objects; hidden/disabled actions match backend authority.</t>
   </si>
   <si>
-    <t>Rejected</t>
-  </si>
-  <si>
     <t>ACC-UI-RM-001 through ACC-UI-RM-008</t>
   </si>
   <si>
+    <t>ACC-RM-006</t>
+  </si>
+  <si>
+    <t>Wave B — Assurance &amp; Close</t>
+  </si>
+  <si>
+    <t>ACC-010</t>
+  </si>
+  <si>
     <t>UI remediation is acceptance evidence where it affects authority, auditability or discoverability.</t>
   </si>
   <si>
-    <t>VALIDATED scope defect; tenant isolation itself is not proven defective. Engineer must confirm the approved entity/book period model and migration impact against implementation SHA before changing schema.</t>
-  </si>
-  <si>
-    <t>ACC-RM-005</t>
-  </si>
-  <si>
-    <t>ACC-001 / ACC-011</t>
-  </si>
-  <si>
-    <t>Period/transaction locks must be scoped to the applicable accounting authority context.</t>
-  </si>
-  <si>
-    <t>PROVEN. LockDate has no demonstrated legal-entity/book scope and lock selection is not entity/book-aware. A separate LockDateOverride request/approval workflow exists, but PostingEngine does not demonstrate consumption of that approved record as execution authority; it instead accepts overrideReason/approvedBy and writes its own override evidence. Frontend exposes override request/history without a corresponding approval action.</t>
-  </si>
-  <si>
-    <t>Returned for remediation</t>
-  </si>
-  <si>
-    <t>LockDate.php and migrations; lock validation/override services/controllers; PostingEngine override validation/logging; FinancialCloseCycleService.php; lockDatesApi.ts; Shared RBAC/approval services; override tests.</t>
-  </si>
-  <si>
-    <t>Acceptance %</t>
-  </si>
-  <si>
-    <t>tenant lock-date migration; LockDate.php; lock validation/override services; FinancialCloseCycleService.php; posting validators consuming lock state.</t>
-  </si>
-  <si>
-    <t>Trace all lock types/setters/overrides/reopen/posting validation and entity/book context. Identify intentionally tenant-wide locks and permission/SoD for override.</t>
-  </si>
-  <si>
-    <t>Define canonical lock scope and one override authority. Entity/book-aware lock evaluation must consume the approved override decision/reference at execution time; PostingEngine must not infer approval from caller-supplied IDs. Align close/reopen and frontend approval workflow; retain explicit tenant-wide locks only where policy defines them.</t>
-  </si>
-  <si>
-    <t>Entity/book lock isolation; approved override required and consumed by ID/version; unapproved/stale/self-approved override blocked; frontend request→approval→retry flow; close/reopen consistency; audit/SoD evidence.</t>
-  </si>
-  <si>
-    <t>VALIDATED at trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. Two override representations currently exist; do not create a third. Cross-link ACC-RM-014/019 and ACC-UI-RM-002.</t>
-  </si>
-  <si>
-    <t>ACC-RM-006</t>
-  </si>
-  <si>
-    <t>Wave B — Assurance &amp; Close</t>
-  </si>
-  <si>
-    <t>ACC-010</t>
-  </si>
-  <si>
     <t>ACC-010 owns the canonical AccountingFinding Registry consumed by Close, Auditor Workspace and Finance AI.</t>
   </si>
   <si>
@@ -895,118 +895,166 @@
     <t>FinancialClose AiFinding.php; fci_ai_findings migrations; FinancialCloseReadinessService.php; finding generation/review services; other assurance/audit/tax finding models.</t>
   </si>
   <si>
+    <t>Accepted ÷ total issues</t>
+  </si>
+  <si>
+    <t>Find every finding/warning/anomaly/control model/table/API. Trace create/status/risk-accept/resolve authority. Prove FCI finding is projection or migrate to canonical ACC-010 without losing history.</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Implement/migrate to canonical ACC-010 AccountingFinding authority. If Financial Close retains a local table, it must be a rebuildable projection with no independent lifecycle/disposition authority. Fix active controller/service contract mismatch and preserve history/audit during migration.</t>
+  </si>
+  <si>
+    <t>Current Result</t>
+  </si>
+  <si>
+    <t>Canonical schema/API and migration mapping; one authoritative disposition path; projection rebuild test if retained; old FCI write path blocked; historical finding lineage preserved; controller/runtime tests.</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>ADR-005 Implementation Conformance / Release Acceptance</t>
+  </si>
+  <si>
+    <t>VALIDATED P0. Financial Close currently behaves as a finding authority, not a proven projection. Engineer discovery must inventory all finding/anomaly models before migration and preserve history.</t>
+  </si>
+  <si>
+    <t>ACC-RM-007</t>
+  </si>
+  <si>
+    <t>ACC-010 / ACC-011</t>
+  </si>
+  <si>
+    <t>Findings used in period close must carry or deterministically resolve applicable tenant/entity/book/period context.</t>
+  </si>
+  <si>
+    <t>PROVEN. AiFinding has no demonstrated period_id/book_id and review_id can be null; AccountReview has entity/book but no period. FinancialCloseAiAnalysisService review lookup is not period-scoped and creates review context with hard-coded book_id='book-001'. FinancialCloseReadinessService queries reviews/open findings by tenant/entity without period/book filters, so other-period/book evidence can contaminate close readiness.</t>
+  </si>
+  <si>
+    <t>AiFinding.php and migrations; AccountReview.php/migrations; FinancialCloseAiAnalysisService.php::ensureReview(); FinancialCloseReadinessService.php; close-cycle/readiness tests.</t>
+  </si>
+  <si>
+    <t>FinancialClose AiFinding.php; FinancialCloseReadinessService.php; AccountReview model/service; close-cycle queries/tests.</t>
+  </si>
+  <si>
+    <t>Trace Finding -&gt; review -&gt; period/entity/book relationship and readiness queries. Prove deterministic context with prior-period/different-book tests; avoid duplicate fields if authoritative relationship already guarantees scope.</t>
+  </si>
+  <si>
+    <t>Bind every close-relevant finding deterministically to tenant/entity/book/period through canonical AccountingFinding context or an authoritative non-null relationship. Remove hard-coded book identity and make readiness queries scope-exact.</t>
+  </si>
+  <si>
+    <t>Prior-period and different-book findings do not contaminate requested close; null review cannot lose scope; no book-001 hard-code; migration/backfill evidence; query tests across multiple periods/books.</t>
+  </si>
+  <si>
+    <t>VALIDATED; prior evidence-gap classification is superseded. Hard-coded book-001 plus period/book-unscoped readiness queries establish a concrete scope defect.</t>
+  </si>
+  <si>
+    <t>ACC-RM-008</t>
+  </si>
+  <si>
     <t>ACC-REM-001 — Pre-Issue Hostile Review &amp; Release Gate</t>
   </si>
   <si>
-    <t>Find every finding/warning/anomaly/control model/table/API. Trace create/status/risk-accept/resolve authority. Prove FCI finding is projection or migrate to canonical ACC-010 without losing history.</t>
+    <t>Mandatory Authority Conjunction: Close may proceed only when all applicable mandatory assurance blockers allow; non-blocking findings may remain.</t>
   </si>
   <si>
     <t>Review Item</t>
   </si>
   <si>
-    <t>Implement/migrate to canonical ACC-010 AccountingFinding authority. If Financial Close retains a local table, it must be a rebuildable projection with no independent lifecycle/disposition authority. Fix active controller/service contract mismatch and preserve history/audit during migration.</t>
+    <t>PROVEN P0 close-control defect. The direct close path re-evaluates FinancialCloseCycleService readiness based on tasks, escalations and signoffs, but open/high-risk assurance findings are not a conjunctive blocker. FinancialCloseReadinessService reports open findings yet its is_ready computation does not require openFindings==0. No separate authoritative risk-acceptance gate is demonstrated in the close execution path.</t>
+  </si>
+  <si>
+    <t>CloseCycleController.php::close(); FinancialCloseCycleService.php::evaluateReadiness()/closeCycle(); FinancialCloseReadinessService.php; AiFinding disposition services; signoff/escalation/task services; risk-acceptance/RBAC searches; tests.</t>
   </si>
   <si>
     <t>Verdict</t>
   </si>
   <si>
-    <t>Canonical schema/API and migration mapping; one authoritative disposition path; projection rebuild test if retained; old FCI write path blocked; historical finding lineage preserved; controller/runtime tests.</t>
-  </si>
-  <si>
-    <t>Accepted ÷ total issues</t>
+    <t>FinancialCloseCycleService.php; FinancialCloseReadinessService.php; close task/signoff/escalation services; canonical assurance/finding services.</t>
   </si>
   <si>
     <t>Finding / Control</t>
   </si>
   <si>
-    <t>Gate</t>
+    <t>Trace every READY_TO_CLOSE/CLOSED path; readiness snapshots; finding disposition/risk acceptance; signoff; stale-state revalidation; reopen. Blocking assurance must gate; advisory must not automatically block.</t>
   </si>
   <si>
     <t>Required Before Issue</t>
   </si>
   <si>
-    <t>Current Result</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
     <t>Current register scope / evidence basis</t>
   </si>
   <si>
-    <t>ADR-005 Implementation Conformance / Release Acceptance</t>
-  </si>
-  <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>VALIDATED P0. Financial Close currently behaves as a finding authority, not a proven projection. Engineer discovery must inventory all finding/anomaly models before migration and preserve history.</t>
-  </si>
-  <si>
-    <t>ACC-RM-007</t>
+    <t>Make close readiness consume canonical assurance disposition as a mandatory conjunction: advisory findings may remain, mandatory blockers must be resolved, and risk acceptance must be a distinct authorised decision. Revalidate current assurance state inside close execution.</t>
+  </si>
+  <si>
+    <t>Mandatory blocker prevents close; advisory does not; approved risk acceptance permits only policy-authorised exception; stale finding/risk state is revalidated; direct close API cannot bypass assurance gate; audit links close decision to evidence.</t>
   </si>
   <si>
     <t>ACC-RM-001–021 plus ACC-UI-RM-001–008 are controlled remediation scope. Proven defects, positive controls and evidence gaps are separated; ADR-005 v1.0 and ACC-REG-001 remain the architecture source of truth.</t>
   </si>
   <si>
-    <t>ACC-010 / ACC-011</t>
-  </si>
-  <si>
     <t>Do not reopen approved architecture through implementation convenience.</t>
   </si>
   <si>
-    <t>Findings used in period close must carry or deterministically resolve applicable tenant/entity/book/period context.</t>
-  </si>
-  <si>
     <t>Engineer-owned discovery</t>
   </si>
   <si>
-    <t>PROVEN. AiFinding has no demonstrated period_id/book_id and review_id can be null; AccountReview has entity/book but no period. FinancialCloseAiAnalysisService review lookup is not period-scoped and creates review context with hard-coded book_id='book-001'. FinancialCloseReadinessService queries reviews/open findings by tenant/entity without period/book filters, so other-period/book evidence can contaminate close readiness.</t>
-  </si>
-  <si>
-    <t>AiFinding.php and migrations; AccountReview.php/migrations; FinancialCloseAiAnalysisService.php::ensureReview(); FinancialCloseReadinessService.php; close-cycle/readiness tests.</t>
-  </si>
-  <si>
     <t>Engineer, not intern report, owns final caller/dependency discovery against the exact implementation branch/SHA. Prior reviewer/intern traces are acceleration evidence only.</t>
   </si>
   <si>
-    <t>FinancialClose AiFinding.php; FinancialCloseReadinessService.php; AccountReview model/service; close-cycle queries/tests.</t>
-  </si>
-  <si>
     <t>Final evidence pack must include immutable SHA and caller/reference inventory with every path disposition.</t>
   </si>
   <si>
-    <t>Trace Finding -&gt; review -&gt; period/entity/book relationship and readiness queries. Prove deterministic context with prior-period/different-book tests; avoid duplicate fields if authoritative relationship already guarantees scope.</t>
+    <t>VALIDATED P0. Close authority must distinguish advisory findings, mandatory blockers and authorised risk acceptance; generic accepted/dismissed AI state is not sufficient risk-acceptance authority.</t>
   </si>
   <si>
     <t>Dependency trace governance</t>
   </si>
   <si>
-    <t>Bind every close-relevant finding deterministically to tenant/entity/book/period through canonical AccountingFinding context or an authoritative non-null relationship. Remove hard-coded book identity and make readiness queries scope-exact.</t>
+    <t>ACC-RM-009</t>
   </si>
   <si>
     <t>PARTIAL and COMPLETE WITH UNRESOLVED EVIDENCE are formally defined. Material PARTIAL trace must be closed by engineer discovery before affected implementation is claimed complete.</t>
   </si>
   <si>
-    <t>Prior-period and different-book findings do not contaminate requested close; null review cannot lose scope; no book-001 hard-code; migration/backfill evidence; query tests across multiple periods/books.</t>
+    <t>ACC-011</t>
   </si>
   <si>
     <t>EVIDENCE_SUBMITTED is prohibited while a material caller/bypass remains unexplained.</t>
   </si>
   <si>
+    <t>Close-cycle state, period lock, lock authority evidence and required events must transition atomically or under an explicit recoverable state machine.</t>
+  </si>
+  <si>
     <t>Batch A — Accounting command authority</t>
   </si>
   <si>
+    <t>PROVEN P0 atomicity defect. closeCycle() persists cycle close, FiscalPeriod lock, LockDate mutation and audit as separate authoritative writes without one enclosing transaction/recoverable state machine. Reopen likewise mutates FiscalPeriod, LockDate, company settings and audit separately. Failure between writes can leave contradictory close/lock state; no required close-completed transactional outbox event is demonstrated.</t>
+  </si>
+  <si>
     <t>Primary implementation cluster: ACC-RM-001, 002, 003, 016 and 019. ACC-RM-010 is an enabling command-outcome contract; ACC-RM-012/021 constraints apply where authoritative events are introduced.</t>
   </si>
   <si>
+    <t>FinancialCloseCycleService.php::closeCycle()/reopen; FiscalPeriod.php; LockDate.php; company_settings lock-date logic; close audit code; event/outbox integrations; close/reopen tests.</t>
+  </si>
+  <si>
+    <t>FinancialCloseCycleService.php; FiscalPeriod.php; LockDate.php; close audit/event/outbox code; close/reopen tests.</t>
+  </si>
+  <si>
     <t>Engineer may discover all rows in parallel, but Batch A architecture changes must be dependency-aware and independently hostile-reviewed.</t>
   </si>
   <si>
-    <t>VALIDATED; prior evidence-gap classification is superseded. Hard-coded book-001 plus period/book-unscoped readiness queries establish a concrete scope defect.</t>
-  </si>
-  <si>
-    <t>ACC-RM-008</t>
+    <t>Trace close/reopen write sequence, transaction/lock boundaries, audit, outbox/events, retries/concurrency. Test failure after each authoritative write and stale-readiness.</t>
+  </si>
+  <si>
+    <t>All P0 remediation items must be independently ACCEPTED and no rejected item remains. ADR-005 itself remains the approved architecture baseline.</t>
   </si>
   <si>
     <t>Batch B — Close / assurance authority</t>
@@ -1015,105 +1063,93 @@
     <t>ACC-RM-004, 005, 006, 007, 008, 009 and 014 form one close-control dependency cluster: scope, finding authority, mandatory blockers, atomic close/reopen and SoD.</t>
   </si>
   <si>
-    <t>Mandatory Authority Conjunction: Close may proceed only when all applicable mandatory assurance blockers allow; non-blocking findings may remain.</t>
+    <t>Execute close/reopen under one authoritative DB transaction or explicitly recoverable state machine, with execution-time readiness/permission revalidation and required event/outbox persistence in the same financial truth boundary.</t>
   </si>
   <si>
     <t>Do not fix close atomicity while leaving readiness/signoff authority bypasses intact.</t>
   </si>
   <si>
-    <t>PROVEN P0 close-control defect. The direct close path re-evaluates FinancialCloseCycleService readiness based on tasks, escalations and signoffs, but open/high-risk assurance findings are not a conjunctive blocker. FinancialCloseReadinessService reports open findings yet its is_ready computation does not require openFindings==0. No separate authoritative risk-acceptance gate is demonstrated in the close execution path.</t>
-  </si>
-  <si>
-    <t>CloseCycleController.php::close(); FinancialCloseCycleService.php::evaluateReadiness()/closeCycle(); FinancialCloseReadinessService.php; AiFinding disposition services; signoff/escalation/task services; risk-acceptance/RBAC searches; tests.</t>
+    <t>Failure injection after every authoritative write; no cycle/period/LockDate/settings contradiction; concurrent close/reopen conflict tests; stale-readiness rejection; retry/idempotency; close/reopen event atomicity.</t>
   </si>
   <si>
     <t>Batch C — Source ingestion / promotion</t>
   </si>
   <si>
-    <t>FinancialCloseCycleService.php; FinancialCloseReadinessService.php; close task/signoff/escalation services; canonical assurance/finding services.</t>
-  </si>
-  <si>
-    <t>Trace every READY_TO_CLOSE/CLOSED path; readiness snapshots; finding disposition/risk acceptance; signoff; stale-state revalidation; reopen. Blocking assurance must gate; advisory must not automatically block.</t>
-  </si>
-  <si>
     <t>ACC-RM-017 and 018 govern human-confirmed source promotion/idempotency and shared staged import. ACC-UI-RM-003/007 are coupled UX/account-mapping controls.</t>
   </si>
   <si>
     <t>No OCR self-promotion and no domain-local import staging engine.</t>
   </si>
   <si>
-    <t>All P0 remediation items must be independently ACCEPTED and no rejected item remains. ADR-005 itself remains the approved architecture baseline.</t>
+    <t>VALIDATED P0. Close and reopen contain multi-write partial-commit paths. Cross-link ACC-RM-012 for transactional publication and ACC-RM-014 for execution authority.</t>
+  </si>
+  <si>
+    <t>ACC-RM-010</t>
   </si>
   <si>
     <t>Batch D — Settlement / reconciliation / evidence</t>
   </si>
   <si>
-    <t>Make close readiness consume canonical assurance disposition as a mandatory conjunction: advisory findings may remain, mandatory blockers must be resolved, and risk acceptance must be a distinct authorised decision. Revalidate current assurance state inside close execution.</t>
-  </si>
-  <si>
-    <t>Mandatory blocker prevents close; advisory does not; approved risk acceptance permits only policy-authorised exception; stale finding/risk state is revalidated; direct close API cannot bypass assurance gate; audit links close decision to evidence.</t>
+    <t>Command results distinguish ACCEPTED/REJECTED/BLOCKED/CONFLICT/FAILED with canonical reason/remediation metadata.</t>
   </si>
   <si>
     <t>ACC-RM-013 and 020 plus ACC-UI-RM-005/006 govern payment-settlement alignment, canonical bank-statement reconciliation and end-to-end evidence drill-down.</t>
   </si>
   <si>
+    <t>PROVEN. PostingResult exposes success plus free-text error instead of canonical ACCEPTED/REJECTED/BLOCKED/CONFLICT/FAILED semantics. Controllers often map materially different conditions such as already-posted, locked period, self-approval and posting failure to the same HTTP 422 shape, preventing deterministic UI/remediation behavior.</t>
+  </si>
+  <si>
     <t>Preserve proven gateway hardening and existing reconciliation matching/unique-line controls.</t>
   </si>
   <si>
+    <t>PostingResult.php; PostingEngine.php; JournalEntriesController and other PostingResult consumers; API exception/error mapping; frontend posting/error handling; lock/reversal/posting tests.</t>
+  </si>
+  <si>
+    <t>PostingResult.php; PostingEngine.php; all PostingResult consumers; controller/API exception mapping; frontend posting-status/error mapping.</t>
+  </si>
+  <si>
     <t>Platform event convergence</t>
   </si>
   <si>
+    <t>Trace every PostingResult consumer; map errors to canonical outcomes/reason codes; preserve compatibility; prove UI/API distinguishes BLOCKED/REJECTED/CONFLICT/FAILED.</t>
+  </si>
+  <si>
     <t>ACC-RM-012 owns transactional publication from financial truth; ACC-RM-021 owns one platform event authority and truthful durable consumer processing.</t>
   </si>
   <si>
     <t>Converge existing mechanisms; do not create an Accounting-local third outbox/event bus.</t>
   </si>
   <si>
+    <t>Introduce one canonical command-result contract with outcome, reason_code, remediation/action metadata, current state/version where applicable, authority/correlation references and retryability. Map existing callers compatibly; do not rely on free-text parsing.</t>
+  </si>
+  <si>
+    <t>Period lock→BLOCKED; stale version/concurrent command→CONFLICT; invalid request/state→REJECTED; infrastructure failure→FAILED; success→ACCEPTED; API/HTTP/UI mappings are deterministic and backwards-compatible where required.</t>
+  </si>
+  <si>
     <t>UI remediation boundary</t>
   </si>
   <si>
-    <t>VALIDATED P0. Close authority must distinguish advisory findings, mandatory blockers and authorised risk acceptance; generic accepted/dismissed AI state is not sufficient risk-acceptance authority.</t>
-  </si>
-  <si>
     <t>ACC-UI-RM-001–008 remain separate UI/UX remediation records. They may be implemented with their governing backend batch but cannot create duplicate business authority.</t>
   </si>
   <si>
+    <t>VALIDATED at immutable trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. This contract is an enabling dependency for ACC-RM-016 conflict UX and ACC-UI-RM-002 locked-period remediation.</t>
+  </si>
+  <si>
     <t>UI acceptance requires backend authority, permission and evidence linkage to remain canonical.</t>
   </si>
   <si>
-    <t>ACC-RM-009</t>
-  </si>
-  <si>
     <t>Evidence closure standard</t>
   </si>
   <si>
-    <t>ACC-011</t>
-  </si>
-  <si>
     <t>Source paths, executable positive/negative tests, runtime results, caller inventory and exact SHA are mandatory; concurrency/atomicity/approval/import/reconciliation/event evidence applies by issue.</t>
   </si>
   <si>
-    <t>Close-cycle state, period lock, lock authority evidence and required events must transition atomically or under an explicit recoverable state machine.</t>
-  </si>
-  <si>
     <t>Screenshot, narrative report or AI claim alone = NOT ACCEPTED.</t>
   </si>
   <si>
-    <t>PROVEN P0 atomicity defect. closeCycle() persists cycle close, FiscalPeriod lock, LockDate mutation and audit as separate authoritative writes without one enclosing transaction/recoverable state machine. Reopen likewise mutates FiscalPeriod, LockDate, company settings and audit separately. Failure between writes can leave contradictory close/lock state; no required close-completed transactional outbox event is demonstrated.</t>
-  </si>
-  <si>
     <t>Independent acceptance</t>
   </si>
   <si>
-    <t>FinancialCloseCycleService.php::closeCycle()/reopen; FiscalPeriod.php; LockDate.php; company_settings lock-date logic; close audit code; event/outbox integrations; close/reopen tests.</t>
-  </si>
-  <si>
-    <t>FinancialCloseCycleService.php; FiscalPeriod.php; LockDate.php; close audit/event/outbox code; close/reopen tests.</t>
-  </si>
-  <si>
-    <t>Trace close/reopen write sequence, transaction/lock boundaries, audit, outbox/events, retries/concurrency. Test failure after each authoritative write and stale-readiness.</t>
-  </si>
-  <si>
     <t>Engineer cannot self-accept. Implementation moves EVIDENCE_SUBMITTED → HOSTILE_REVIEW → ACCEPTED/REJECTED only after independent code/test/evidence verification.</t>
   </si>
   <si>
@@ -1123,49 +1159,52 @@
     <t>P0 sequencing</t>
   </si>
   <si>
-    <t>Execute close/reopen under one authoritative DB transaction or explicitly recoverable state machine, with execution-time readiness/permission revalidation and required event/outbox persistence in the same financial truth boundary.</t>
+    <t>ACC-RM-011</t>
   </si>
   <si>
     <t>CONDITIONAL PASS</t>
   </si>
   <si>
-    <t>Failure injection after every authoritative write; no cycle/period/LockDate/settings contradiction; concurrent close/reopen conflict tests; stale-readiness rejection; retry/idempotency; close/reopen event atomicity.</t>
-  </si>
-  <si>
     <t>Discovery may proceed across all remediation rows. Implementation must follow dependency-aware batches; later-batch work may not silently redesign Batch A shared authority or bypass an unresolved P0 dependency.</t>
   </si>
   <si>
+    <t>Journal business, workflow, approval and posting states are distinct state dimensions.</t>
+  </si>
+  <si>
     <t>Engineer records dependency conflicts/contradictions before coding across the boundary.</t>
   </si>
   <si>
+    <t>PROVEN. JournalEntry primarily has status=draft|posted plus correction-oriented lifecycle_status/version flags; no independent business/workflow/approval/posting state dimensions are demonstrated. Manual journal posting can move draft directly to posted once current permission/lock checks pass, with no journal-specific Shared Approval decision consumed.</t>
+  </si>
+  <si>
+    <t>JournalEntry.php and migrations; ManualJournalPostingService.php; journal controllers/routes; PostingEngine.php; correction lifecycle migrations; Shared Approval integrations/search; journal UI/tests.</t>
+  </si>
+  <si>
     <t>Final issue decision</t>
   </si>
   <si>
+    <t>JournalEntry.php; journal migrations; PostingEngine.php; journal services/controllers; workflow/approval integrations; tests.</t>
+  </si>
+  <si>
     <t>APPROVE TO ISSUE — ENGINEER DISCOVERY + BATCHED IMPLEMENTATION</t>
   </si>
   <si>
-    <t>VALIDATED P0. Close and reopen contain multi-write partial-commit paths. Cross-link ACC-RM-012 for transactional publication and ACC-RM-014 for execution authority.</t>
+    <t>Trace every status/lifecycle_status read/write; enumerate values; map to business/workflow/approval/posting dimensions; identify report/UI/API dependencies before migration.</t>
   </si>
   <si>
     <t>ACC-REM-001 is approved as the controlled remediation/evidence register for engineer-owned discovery and phased implementation. This is not implementation acceptance and does not change ADR-005 approval status.</t>
   </si>
   <si>
-    <t>ACC-RM-010</t>
-  </si>
-  <si>
     <t>Begin with engineer repository discovery and Batch A; each batch requires independent hostile acceptance.</t>
   </si>
   <si>
+    <t>Define distinct journal business, workflow, approval and posting dimensions or prove an equivalent canonical model. Integrate journal approval with Shared Approval/Workflow and ACC-RM-019; material edits must invalidate/rebind approvals as policy requires.</t>
+  </si>
+  <si>
     <t>MANDATORY ENGINEER INSTRUCTIONS</t>
   </si>
   <si>
-    <t>Command results distinguish ACCEPTED/REJECTED/BLOCKED/CONFLICT/FAILED with canonical reason/remediation metadata.</t>
-  </si>
-  <si>
-    <t>PROVEN. PostingResult exposes success plus free-text error instead of canonical ACCEPTED/REJECTED/BLOCKED/CONFLICT/FAILED semantics. Controllers often map materially different conditions such as already-posted, locked period, self-approval and posting failure to the same HTTP 422 shape, preventing deterministic UI/remediation behavior.</t>
-  </si>
-  <si>
-    <t>PostingResult.php; PostingEngine.php; JournalEntriesController and other PostingResult consumers; API exception/error mapping; frontend posting/error handling; lock/reversal/posting tests.</t>
+    <t>State migration map and transition matrix; independent approval/posting tests; draft cannot post when approval required; material edit invalidates stale approval; reporting/API/UI compatibility; correction lifecycle remains distinct.</t>
   </si>
   <si>
     <t>1. Work from an exact branch and commit SHA.
@@ -1179,49 +1218,10 @@
 9. ACCEPTED is set only by independent hostile review.</t>
   </si>
   <si>
-    <t>PostingResult.php; PostingEngine.php; all PostingResult consumers; controller/API exception mapping; frontend posting-status/error mapping.</t>
-  </si>
-  <si>
     <t>Execution rule</t>
   </si>
   <si>
-    <t>Trace every PostingResult consumer; map errors to canonical outcomes/reason codes; preserve compatibility; prove UI/API distinguishes BLOCKED/REJECTED/CONFLICT/FAILED.</t>
-  </si>
-  <si>
     <t>Discovery first within each changed authority; controlled replacement path second; migrate callers; disable bypass; prove old failure path; submit evidence.</t>
-  </si>
-  <si>
-    <t>Introduce one canonical command-result contract with outcome, reason_code, remediation/action metadata, current state/version where applicable, authority/correlation references and retryability. Map existing callers compatibly; do not rely on free-text parsing.</t>
-  </si>
-  <si>
-    <t>Period lock→BLOCKED; stale version/concurrent command→CONFLICT; invalid request/state→REJECTED; infrastructure failure→FAILED; success→ACCEPTED; API/HTTP/UI mappings are deterministic and backwards-compatible where required.</t>
-  </si>
-  <si>
-    <t>VALIDATED at immutable trace baseline 5bb8de27d7c9e47cb312c240dc1119d42fba5a3a. This contract is an enabling dependency for ACC-RM-016 conflict UX and ACC-UI-RM-002 locked-period remediation.</t>
-  </si>
-  <si>
-    <t>ACC-RM-011</t>
-  </si>
-  <si>
-    <t>Journal business, workflow, approval and posting states are distinct state dimensions.</t>
-  </si>
-  <si>
-    <t>PROVEN. JournalEntry primarily has status=draft|posted plus correction-oriented lifecycle_status/version flags; no independent business/workflow/approval/posting state dimensions are demonstrated. Manual journal posting can move draft directly to posted once current permission/lock checks pass, with no journal-specific Shared Approval decision consumed.</t>
-  </si>
-  <si>
-    <t>JournalEntry.php and migrations; ManualJournalPostingService.php; journal controllers/routes; PostingEngine.php; correction lifecycle migrations; Shared Approval integrations/search; journal UI/tests.</t>
-  </si>
-  <si>
-    <t>JournalEntry.php; journal migrations; PostingEngine.php; journal services/controllers; workflow/approval integrations; tests.</t>
-  </si>
-  <si>
-    <t>Trace every status/lifecycle_status read/write; enumerate values; map to business/workflow/approval/posting dimensions; identify report/UI/API dependencies before migration.</t>
-  </si>
-  <si>
-    <t>Define distinct journal business, workflow, approval and posting dimensions or prove an equivalent canonical model. Integrate journal approval with Shared Approval/Workflow and ACC-RM-019; material edits must invalidate/rebind approvals as policy requires.</t>
-  </si>
-  <si>
-    <t>State migration map and transition matrix; independent approval/posting tests; draft cannot post when approval required; material edit invalidates stale approval; reporting/API/UI compatibility; correction lifecycle remains distinct.</t>
   </si>
   <si>
     <t>VALIDATED. Current journal lifecycle fields do not prove independent workflow/approval/posting state. Cross-link ACC-RM-019; do not create an Accounting-local workflow engine.</t>
@@ -1820,6 +1820,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
@@ -1827,11 +1832,6 @@
     </font>
     <font>
       <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1888,39 +1888,39 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2153,6 +2153,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -2171,151 +2172,151 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
+      <c r="A1" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>7</v>
+      <c r="A2" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>11</v>
+      <c r="A3" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="R5" s="10" t="s">
-        <v>123</v>
+        <v>14</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="V5" s="12">
         <v>46248.0</v>
@@ -2323,67 +2324,67 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>150</v>
-      </c>
       <c r="U6" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="V6" s="12">
         <v>46248.0</v>
@@ -2391,67 +2392,67 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>214</v>
+      <c r="G7" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>212</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="J7" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>128</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="V7" s="12">
         <v>46248.0</v>
@@ -2459,67 +2460,67 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="G8" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>263</v>
-      </c>
       <c r="N8" s="9" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="V8" s="12">
         <v>46248.0</v>
@@ -2527,67 +2528,67 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="V9" s="12">
         <v>46248.0</v>
@@ -2595,16 +2596,16 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>287</v>
-      </c>
       <c r="D10" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>288</v>
@@ -2625,10 +2626,10 @@
         <v>128</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>295</v>
@@ -2637,25 +2638,25 @@
         <v>297</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="V10" s="12">
         <v>46248.0</v>
@@ -2663,67 +2664,67 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="V11" s="12">
         <v>46248.0</v>
@@ -2731,67 +2732,67 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="V12" s="12">
         <v>46248.0</v>
@@ -2799,67 +2800,67 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="V13" s="12">
         <v>46248.0</v>
@@ -2867,67 +2868,67 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="V14" s="12">
         <v>46248.0</v>
@@ -2935,64 +2936,64 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U15" s="9" t="s">
         <v>399</v>
@@ -3006,13 +3007,13 @@
         <v>400</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>401</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>402</v>
@@ -3033,10 +3034,10 @@
         <v>128</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>407</v>
@@ -3045,22 +3046,22 @@
         <v>408</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U16" s="9" t="s">
         <v>409</v>
@@ -3080,7 +3081,7 @@
         <v>412</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>413</v>
@@ -3101,10 +3102,10 @@
         <v>128</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>418</v>
@@ -3113,22 +3114,22 @@
         <v>419</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U17" s="9" t="s">
         <v>420</v>
@@ -3142,13 +3143,13 @@
         <v>421</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>422</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>423</v>
@@ -3169,10 +3170,10 @@
         <v>128</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>428</v>
@@ -3181,22 +3182,22 @@
         <v>429</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U18" s="9" t="s">
         <v>430</v>
@@ -3210,13 +3211,13 @@
         <v>431</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>432</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>433</v>
@@ -3237,10 +3238,10 @@
         <v>128</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>438</v>
@@ -3249,22 +3250,22 @@
         <v>439</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U19" s="9" t="s">
         <v>440</v>
@@ -3278,13 +3279,13 @@
         <v>441</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>442</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>443</v>
@@ -3315,16 +3316,16 @@
       <c r="O20" s="14"/>
       <c r="P20" s="14"/>
       <c r="Q20" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U20" s="9" t="s">
         <v>450</v>
@@ -3338,13 +3339,13 @@
         <v>451</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>452</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>453</v>
@@ -3375,16 +3376,16 @@
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U21" s="9" t="s">
         <v>460</v>
@@ -3398,13 +3399,13 @@
         <v>461</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>462</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>463</v>
@@ -3435,16 +3436,16 @@
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U22" s="9" t="s">
         <v>470</v>
@@ -3458,13 +3459,13 @@
         <v>471</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>472</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>473</v>
@@ -3495,16 +3496,16 @@
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U23" s="9" t="s">
         <v>480</v>
@@ -3515,16 +3516,16 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>481</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>482</v>
@@ -3555,16 +3556,16 @@
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>489</v>
@@ -3578,13 +3579,13 @@
         <v>490</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>491</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>492</v>
@@ -3615,16 +3616,16 @@
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U25" s="9" t="s">
         <v>499</v>
@@ -3644,7 +3645,7 @@
         <v>502</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>503</v>
@@ -3675,16 +3676,16 @@
       <c r="O26" s="14"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U26" s="9" t="s">
         <v>510</v>
@@ -3704,7 +3705,7 @@
         <v>513</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>514</v>
@@ -3735,16 +3736,16 @@
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R27" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U27" s="9" t="s">
         <v>521</v>
@@ -3764,7 +3765,7 @@
         <v>524</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>525</v>
@@ -3795,16 +3796,16 @@
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R28" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U28" s="9" t="s">
         <v>532</v>
@@ -3824,7 +3825,7 @@
         <v>535</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>536</v>
@@ -3855,16 +3856,16 @@
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R29" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U29" s="9" t="s">
         <v>543</v>
@@ -3884,7 +3885,7 @@
         <v>546</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>547</v>
@@ -3915,16 +3916,16 @@
       <c r="O30" s="14"/>
       <c r="P30" s="14"/>
       <c r="Q30" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R30" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>554</v>
@@ -3944,7 +3945,7 @@
         <v>557</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>558</v>
@@ -3975,16 +3976,16 @@
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U31" s="9" t="s">
         <v>565</v>
@@ -4004,7 +4005,7 @@
         <v>568</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>569</v>
@@ -4022,7 +4023,7 @@
         <v>573</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
@@ -4035,16 +4036,16 @@
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R32" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>576</v>
@@ -4064,7 +4065,7 @@
         <v>579</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>580</v>
@@ -4082,7 +4083,7 @@
         <v>584</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
@@ -4095,16 +4096,16 @@
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R33" s="9" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="U33" s="9" t="s">
         <v>587</v>
@@ -4114,1873 +4115,1873 @@
       </c>
     </row>
     <row r="34">
-      <c r="J34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
+      <c r="J34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
     </row>
     <row r="35">
-      <c r="J35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
+      <c r="J35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
     </row>
     <row r="36">
-      <c r="J36" s="11"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
+      <c r="J36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
     </row>
     <row r="37">
-      <c r="J37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
-      <c r="T37" s="11"/>
+      <c r="J37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
     </row>
     <row r="38">
-      <c r="J38" s="11"/>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
-      <c r="T38" s="11"/>
+      <c r="J38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
     </row>
     <row r="39">
-      <c r="J39" s="11"/>
-      <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
-      <c r="T39" s="11"/>
+      <c r="J39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
     </row>
     <row r="40">
-      <c r="J40" s="11"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
-      <c r="T40" s="11"/>
+      <c r="J40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
     </row>
     <row r="41">
-      <c r="J41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-      <c r="T41" s="11"/>
+      <c r="J41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
     </row>
     <row r="42">
-      <c r="J42" s="11"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
-      <c r="T42" s="11"/>
+      <c r="J42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
     </row>
     <row r="43">
-      <c r="J43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
-      <c r="T43" s="11"/>
+      <c r="J43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
     </row>
     <row r="44">
-      <c r="J44" s="11"/>
-      <c r="Q44" s="11"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
-      <c r="T44" s="11"/>
+      <c r="J44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
     </row>
     <row r="45">
-      <c r="J45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
+      <c r="J45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
     </row>
     <row r="46">
-      <c r="J46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-      <c r="T46" s="11"/>
+      <c r="J46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
     </row>
     <row r="47">
-      <c r="J47" s="11"/>
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
-      <c r="T47" s="11"/>
+      <c r="J47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
     </row>
     <row r="48">
-      <c r="J48" s="11"/>
-      <c r="Q48" s="11"/>
-      <c r="R48" s="11"/>
-      <c r="S48" s="11"/>
-      <c r="T48" s="11"/>
+      <c r="J48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
     </row>
     <row r="49">
-      <c r="J49" s="11"/>
-      <c r="Q49" s="11"/>
-      <c r="R49" s="11"/>
-      <c r="S49" s="11"/>
-      <c r="T49" s="11"/>
+      <c r="J49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
     </row>
     <row r="50">
-      <c r="J50" s="11"/>
-      <c r="Q50" s="11"/>
-      <c r="R50" s="11"/>
-      <c r="S50" s="11"/>
-      <c r="T50" s="11"/>
+      <c r="J50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
     </row>
     <row r="51">
-      <c r="J51" s="11"/>
-      <c r="Q51" s="11"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="11"/>
-      <c r="T51" s="11"/>
+      <c r="J51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
     </row>
     <row r="52">
-      <c r="J52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="11"/>
-      <c r="T52" s="11"/>
+      <c r="J52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
     </row>
     <row r="53">
-      <c r="J53" s="11"/>
-      <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
-      <c r="S53" s="11"/>
-      <c r="T53" s="11"/>
+      <c r="J53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
     </row>
     <row r="54">
-      <c r="J54" s="11"/>
-      <c r="Q54" s="11"/>
-      <c r="R54" s="11"/>
-      <c r="S54" s="11"/>
-      <c r="T54" s="11"/>
+      <c r="J54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
     </row>
     <row r="55">
-      <c r="J55" s="11"/>
-      <c r="Q55" s="11"/>
-      <c r="R55" s="11"/>
-      <c r="S55" s="11"/>
-      <c r="T55" s="11"/>
+      <c r="J55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
     </row>
     <row r="56">
-      <c r="J56" s="11"/>
-      <c r="Q56" s="11"/>
-      <c r="R56" s="11"/>
-      <c r="S56" s="11"/>
-      <c r="T56" s="11"/>
+      <c r="J56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
     </row>
     <row r="57">
-      <c r="J57" s="11"/>
-      <c r="Q57" s="11"/>
-      <c r="R57" s="11"/>
-      <c r="S57" s="11"/>
-      <c r="T57" s="11"/>
+      <c r="J57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
     </row>
     <row r="58">
-      <c r="J58" s="11"/>
-      <c r="Q58" s="11"/>
-      <c r="R58" s="11"/>
-      <c r="S58" s="11"/>
-      <c r="T58" s="11"/>
+      <c r="J58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
     </row>
     <row r="59">
-      <c r="J59" s="11"/>
-      <c r="Q59" s="11"/>
-      <c r="R59" s="11"/>
-      <c r="S59" s="11"/>
-      <c r="T59" s="11"/>
+      <c r="J59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
     </row>
     <row r="60">
-      <c r="J60" s="11"/>
-      <c r="Q60" s="11"/>
-      <c r="R60" s="11"/>
-      <c r="S60" s="11"/>
-      <c r="T60" s="11"/>
+      <c r="J60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
     </row>
     <row r="61">
-      <c r="J61" s="11"/>
-      <c r="Q61" s="11"/>
-      <c r="R61" s="11"/>
-      <c r="S61" s="11"/>
-      <c r="T61" s="11"/>
+      <c r="J61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
     </row>
     <row r="62">
-      <c r="J62" s="11"/>
-      <c r="Q62" s="11"/>
-      <c r="R62" s="11"/>
-      <c r="S62" s="11"/>
-      <c r="T62" s="11"/>
+      <c r="J62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
     </row>
     <row r="63">
-      <c r="J63" s="11"/>
-      <c r="Q63" s="11"/>
-      <c r="R63" s="11"/>
-      <c r="S63" s="11"/>
-      <c r="T63" s="11"/>
+      <c r="J63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
     </row>
     <row r="64">
-      <c r="J64" s="11"/>
-      <c r="Q64" s="11"/>
-      <c r="R64" s="11"/>
-      <c r="S64" s="11"/>
-      <c r="T64" s="11"/>
+      <c r="J64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
     </row>
     <row r="65">
-      <c r="J65" s="11"/>
-      <c r="Q65" s="11"/>
-      <c r="R65" s="11"/>
-      <c r="S65" s="11"/>
-      <c r="T65" s="11"/>
+      <c r="J65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
     </row>
     <row r="66">
-      <c r="J66" s="11"/>
-      <c r="Q66" s="11"/>
-      <c r="R66" s="11"/>
-      <c r="S66" s="11"/>
-      <c r="T66" s="11"/>
+      <c r="J66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
     </row>
     <row r="67">
-      <c r="J67" s="11"/>
-      <c r="Q67" s="11"/>
-      <c r="R67" s="11"/>
-      <c r="S67" s="11"/>
-      <c r="T67" s="11"/>
+      <c r="J67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
     </row>
     <row r="68">
-      <c r="J68" s="11"/>
-      <c r="Q68" s="11"/>
-      <c r="R68" s="11"/>
-      <c r="S68" s="11"/>
-      <c r="T68" s="11"/>
+      <c r="J68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
     </row>
     <row r="69">
-      <c r="J69" s="11"/>
-      <c r="Q69" s="11"/>
-      <c r="R69" s="11"/>
-      <c r="S69" s="11"/>
-      <c r="T69" s="11"/>
+      <c r="J69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
     </row>
     <row r="70">
-      <c r="J70" s="11"/>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="11"/>
-      <c r="S70" s="11"/>
-      <c r="T70" s="11"/>
+      <c r="J70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
     </row>
     <row r="71">
-      <c r="J71" s="11"/>
-      <c r="Q71" s="11"/>
-      <c r="R71" s="11"/>
-      <c r="S71" s="11"/>
-      <c r="T71" s="11"/>
+      <c r="J71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
     </row>
     <row r="72">
-      <c r="J72" s="11"/>
-      <c r="Q72" s="11"/>
-      <c r="R72" s="11"/>
-      <c r="S72" s="11"/>
-      <c r="T72" s="11"/>
+      <c r="J72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
     </row>
     <row r="73">
-      <c r="J73" s="11"/>
-      <c r="Q73" s="11"/>
-      <c r="R73" s="11"/>
-      <c r="S73" s="11"/>
-      <c r="T73" s="11"/>
+      <c r="J73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
     </row>
     <row r="74">
-      <c r="J74" s="11"/>
-      <c r="Q74" s="11"/>
-      <c r="R74" s="11"/>
-      <c r="S74" s="11"/>
-      <c r="T74" s="11"/>
+      <c r="J74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="10"/>
     </row>
     <row r="75">
-      <c r="J75" s="11"/>
-      <c r="Q75" s="11"/>
-      <c r="R75" s="11"/>
-      <c r="S75" s="11"/>
-      <c r="T75" s="11"/>
+      <c r="J75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
     </row>
     <row r="76">
-      <c r="J76" s="11"/>
-      <c r="Q76" s="11"/>
-      <c r="R76" s="11"/>
-      <c r="S76" s="11"/>
-      <c r="T76" s="11"/>
+      <c r="J76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="10"/>
     </row>
     <row r="77">
-      <c r="J77" s="11"/>
-      <c r="Q77" s="11"/>
-      <c r="R77" s="11"/>
-      <c r="S77" s="11"/>
-      <c r="T77" s="11"/>
+      <c r="J77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
     </row>
     <row r="78">
-      <c r="J78" s="11"/>
-      <c r="Q78" s="11"/>
-      <c r="R78" s="11"/>
-      <c r="S78" s="11"/>
-      <c r="T78" s="11"/>
+      <c r="J78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="10"/>
     </row>
     <row r="79">
-      <c r="J79" s="11"/>
-      <c r="Q79" s="11"/>
-      <c r="R79" s="11"/>
-      <c r="S79" s="11"/>
-      <c r="T79" s="11"/>
+      <c r="J79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
     </row>
     <row r="80">
-      <c r="J80" s="11"/>
-      <c r="Q80" s="11"/>
-      <c r="R80" s="11"/>
-      <c r="S80" s="11"/>
-      <c r="T80" s="11"/>
+      <c r="J80" s="10"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
+      <c r="S80" s="10"/>
+      <c r="T80" s="10"/>
     </row>
     <row r="81">
-      <c r="J81" s="11"/>
-      <c r="Q81" s="11"/>
-      <c r="R81" s="11"/>
-      <c r="S81" s="11"/>
-      <c r="T81" s="11"/>
+      <c r="J81" s="10"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
     </row>
     <row r="82">
-      <c r="J82" s="11"/>
-      <c r="Q82" s="11"/>
-      <c r="R82" s="11"/>
-      <c r="S82" s="11"/>
-      <c r="T82" s="11"/>
+      <c r="J82" s="10"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
+      <c r="S82" s="10"/>
+      <c r="T82" s="10"/>
     </row>
     <row r="83">
-      <c r="J83" s="11"/>
-      <c r="Q83" s="11"/>
-      <c r="R83" s="11"/>
-      <c r="S83" s="11"/>
-      <c r="T83" s="11"/>
+      <c r="J83" s="10"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
     </row>
     <row r="84">
-      <c r="J84" s="11"/>
-      <c r="Q84" s="11"/>
-      <c r="R84" s="11"/>
-      <c r="S84" s="11"/>
-      <c r="T84" s="11"/>
+      <c r="J84" s="10"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
+      <c r="S84" s="10"/>
+      <c r="T84" s="10"/>
     </row>
     <row r="85">
-      <c r="J85" s="11"/>
-      <c r="Q85" s="11"/>
-      <c r="R85" s="11"/>
-      <c r="S85" s="11"/>
-      <c r="T85" s="11"/>
+      <c r="J85" s="10"/>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
     </row>
     <row r="86">
-      <c r="J86" s="11"/>
-      <c r="Q86" s="11"/>
-      <c r="R86" s="11"/>
-      <c r="S86" s="11"/>
-      <c r="T86" s="11"/>
+      <c r="J86" s="10"/>
+      <c r="Q86" s="10"/>
+      <c r="R86" s="10"/>
+      <c r="S86" s="10"/>
+      <c r="T86" s="10"/>
     </row>
     <row r="87">
-      <c r="J87" s="11"/>
-      <c r="Q87" s="11"/>
-      <c r="R87" s="11"/>
-      <c r="S87" s="11"/>
-      <c r="T87" s="11"/>
+      <c r="J87" s="10"/>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
     </row>
     <row r="88">
-      <c r="J88" s="11"/>
-      <c r="Q88" s="11"/>
-      <c r="R88" s="11"/>
-      <c r="S88" s="11"/>
-      <c r="T88" s="11"/>
+      <c r="J88" s="10"/>
+      <c r="Q88" s="10"/>
+      <c r="R88" s="10"/>
+      <c r="S88" s="10"/>
+      <c r="T88" s="10"/>
     </row>
     <row r="89">
-      <c r="J89" s="11"/>
-      <c r="Q89" s="11"/>
-      <c r="R89" s="11"/>
-      <c r="S89" s="11"/>
-      <c r="T89" s="11"/>
+      <c r="J89" s="10"/>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
     </row>
     <row r="90">
-      <c r="J90" s="11"/>
-      <c r="Q90" s="11"/>
-      <c r="R90" s="11"/>
-      <c r="S90" s="11"/>
-      <c r="T90" s="11"/>
+      <c r="J90" s="10"/>
+      <c r="Q90" s="10"/>
+      <c r="R90" s="10"/>
+      <c r="S90" s="10"/>
+      <c r="T90" s="10"/>
     </row>
     <row r="91">
-      <c r="J91" s="11"/>
-      <c r="Q91" s="11"/>
-      <c r="R91" s="11"/>
-      <c r="S91" s="11"/>
-      <c r="T91" s="11"/>
+      <c r="J91" s="10"/>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
     </row>
     <row r="92">
-      <c r="J92" s="11"/>
-      <c r="Q92" s="11"/>
-      <c r="R92" s="11"/>
-      <c r="S92" s="11"/>
-      <c r="T92" s="11"/>
+      <c r="J92" s="10"/>
+      <c r="Q92" s="10"/>
+      <c r="R92" s="10"/>
+      <c r="S92" s="10"/>
+      <c r="T92" s="10"/>
     </row>
     <row r="93">
-      <c r="J93" s="11"/>
-      <c r="Q93" s="11"/>
-      <c r="R93" s="11"/>
-      <c r="S93" s="11"/>
-      <c r="T93" s="11"/>
+      <c r="J93" s="10"/>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
     </row>
     <row r="94">
-      <c r="J94" s="11"/>
-      <c r="Q94" s="11"/>
-      <c r="R94" s="11"/>
-      <c r="S94" s="11"/>
-      <c r="T94" s="11"/>
+      <c r="J94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="10"/>
     </row>
     <row r="95">
-      <c r="J95" s="11"/>
-      <c r="Q95" s="11"/>
-      <c r="R95" s="11"/>
-      <c r="S95" s="11"/>
-      <c r="T95" s="11"/>
+      <c r="J95" s="10"/>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
     </row>
     <row r="96">
-      <c r="J96" s="11"/>
-      <c r="Q96" s="11"/>
-      <c r="R96" s="11"/>
-      <c r="S96" s="11"/>
-      <c r="T96" s="11"/>
+      <c r="J96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10"/>
+      <c r="S96" s="10"/>
+      <c r="T96" s="10"/>
     </row>
     <row r="97">
-      <c r="J97" s="11"/>
-      <c r="Q97" s="11"/>
-      <c r="R97" s="11"/>
-      <c r="S97" s="11"/>
-      <c r="T97" s="11"/>
+      <c r="J97" s="10"/>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
     </row>
     <row r="98">
-      <c r="J98" s="11"/>
-      <c r="Q98" s="11"/>
-      <c r="R98" s="11"/>
-      <c r="S98" s="11"/>
-      <c r="T98" s="11"/>
+      <c r="J98" s="10"/>
+      <c r="Q98" s="10"/>
+      <c r="R98" s="10"/>
+      <c r="S98" s="10"/>
+      <c r="T98" s="10"/>
     </row>
     <row r="99">
-      <c r="J99" s="11"/>
-      <c r="Q99" s="11"/>
-      <c r="R99" s="11"/>
-      <c r="S99" s="11"/>
-      <c r="T99" s="11"/>
+      <c r="J99" s="10"/>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
     </row>
     <row r="100">
-      <c r="J100" s="11"/>
-      <c r="Q100" s="11"/>
-      <c r="R100" s="11"/>
-      <c r="S100" s="11"/>
-      <c r="T100" s="11"/>
+      <c r="J100" s="10"/>
+      <c r="Q100" s="10"/>
+      <c r="R100" s="10"/>
+      <c r="S100" s="10"/>
+      <c r="T100" s="10"/>
     </row>
     <row r="101">
-      <c r="J101" s="11"/>
-      <c r="Q101" s="11"/>
-      <c r="R101" s="11"/>
-      <c r="S101" s="11"/>
-      <c r="T101" s="11"/>
+      <c r="J101" s="10"/>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
     </row>
     <row r="102">
-      <c r="J102" s="11"/>
-      <c r="Q102" s="11"/>
-      <c r="R102" s="11"/>
-      <c r="S102" s="11"/>
-      <c r="T102" s="11"/>
+      <c r="J102" s="10"/>
+      <c r="Q102" s="10"/>
+      <c r="R102" s="10"/>
+      <c r="S102" s="10"/>
+      <c r="T102" s="10"/>
     </row>
     <row r="103">
-      <c r="J103" s="11"/>
-      <c r="Q103" s="11"/>
-      <c r="R103" s="11"/>
-      <c r="S103" s="11"/>
-      <c r="T103" s="11"/>
+      <c r="J103" s="10"/>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="10"/>
+      <c r="S103" s="10"/>
+      <c r="T103" s="10"/>
     </row>
     <row r="104">
-      <c r="J104" s="11"/>
-      <c r="Q104" s="11"/>
-      <c r="R104" s="11"/>
-      <c r="S104" s="11"/>
-      <c r="T104" s="11"/>
+      <c r="J104" s="10"/>
+      <c r="Q104" s="10"/>
+      <c r="R104" s="10"/>
+      <c r="S104" s="10"/>
+      <c r="T104" s="10"/>
     </row>
     <row r="105">
-      <c r="J105" s="11"/>
-      <c r="Q105" s="11"/>
-      <c r="R105" s="11"/>
-      <c r="S105" s="11"/>
-      <c r="T105" s="11"/>
+      <c r="J105" s="10"/>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
     </row>
     <row r="106">
-      <c r="J106" s="11"/>
-      <c r="Q106" s="11"/>
-      <c r="R106" s="11"/>
-      <c r="S106" s="11"/>
-      <c r="T106" s="11"/>
+      <c r="J106" s="10"/>
+      <c r="Q106" s="10"/>
+      <c r="R106" s="10"/>
+      <c r="S106" s="10"/>
+      <c r="T106" s="10"/>
     </row>
     <row r="107">
-      <c r="J107" s="11"/>
-      <c r="Q107" s="11"/>
-      <c r="R107" s="11"/>
-      <c r="S107" s="11"/>
-      <c r="T107" s="11"/>
+      <c r="J107" s="10"/>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
     </row>
     <row r="108">
-      <c r="J108" s="11"/>
-      <c r="Q108" s="11"/>
-      <c r="R108" s="11"/>
-      <c r="S108" s="11"/>
-      <c r="T108" s="11"/>
+      <c r="J108" s="10"/>
+      <c r="Q108" s="10"/>
+      <c r="R108" s="10"/>
+      <c r="S108" s="10"/>
+      <c r="T108" s="10"/>
     </row>
     <row r="109">
-      <c r="J109" s="11"/>
-      <c r="Q109" s="11"/>
-      <c r="R109" s="11"/>
-      <c r="S109" s="11"/>
-      <c r="T109" s="11"/>
+      <c r="J109" s="10"/>
+      <c r="Q109" s="10"/>
+      <c r="R109" s="10"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="10"/>
     </row>
     <row r="110">
-      <c r="J110" s="11"/>
-      <c r="Q110" s="11"/>
-      <c r="R110" s="11"/>
-      <c r="S110" s="11"/>
-      <c r="T110" s="11"/>
+      <c r="J110" s="10"/>
+      <c r="Q110" s="10"/>
+      <c r="R110" s="10"/>
+      <c r="S110" s="10"/>
+      <c r="T110" s="10"/>
     </row>
     <row r="111">
-      <c r="J111" s="11"/>
-      <c r="Q111" s="11"/>
-      <c r="R111" s="11"/>
-      <c r="S111" s="11"/>
-      <c r="T111" s="11"/>
+      <c r="J111" s="10"/>
+      <c r="Q111" s="10"/>
+      <c r="R111" s="10"/>
+      <c r="S111" s="10"/>
+      <c r="T111" s="10"/>
     </row>
     <row r="112">
-      <c r="J112" s="11"/>
-      <c r="Q112" s="11"/>
-      <c r="R112" s="11"/>
-      <c r="S112" s="11"/>
-      <c r="T112" s="11"/>
+      <c r="J112" s="10"/>
+      <c r="Q112" s="10"/>
+      <c r="R112" s="10"/>
+      <c r="S112" s="10"/>
+      <c r="T112" s="10"/>
     </row>
     <row r="113">
-      <c r="J113" s="11"/>
-      <c r="Q113" s="11"/>
-      <c r="R113" s="11"/>
-      <c r="S113" s="11"/>
-      <c r="T113" s="11"/>
+      <c r="J113" s="10"/>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="10"/>
+      <c r="S113" s="10"/>
+      <c r="T113" s="10"/>
     </row>
     <row r="114">
-      <c r="J114" s="11"/>
-      <c r="Q114" s="11"/>
-      <c r="R114" s="11"/>
-      <c r="S114" s="11"/>
-      <c r="T114" s="11"/>
+      <c r="J114" s="10"/>
+      <c r="Q114" s="10"/>
+      <c r="R114" s="10"/>
+      <c r="S114" s="10"/>
+      <c r="T114" s="10"/>
     </row>
     <row r="115">
-      <c r="J115" s="11"/>
-      <c r="Q115" s="11"/>
-      <c r="R115" s="11"/>
-      <c r="S115" s="11"/>
-      <c r="T115" s="11"/>
+      <c r="J115" s="10"/>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
     </row>
     <row r="116">
-      <c r="J116" s="11"/>
-      <c r="Q116" s="11"/>
-      <c r="R116" s="11"/>
-      <c r="S116" s="11"/>
-      <c r="T116" s="11"/>
+      <c r="J116" s="10"/>
+      <c r="Q116" s="10"/>
+      <c r="R116" s="10"/>
+      <c r="S116" s="10"/>
+      <c r="T116" s="10"/>
     </row>
     <row r="117">
-      <c r="J117" s="11"/>
-      <c r="Q117" s="11"/>
-      <c r="R117" s="11"/>
-      <c r="S117" s="11"/>
-      <c r="T117" s="11"/>
+      <c r="J117" s="10"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="10"/>
+      <c r="S117" s="10"/>
+      <c r="T117" s="10"/>
     </row>
     <row r="118">
-      <c r="J118" s="11"/>
-      <c r="Q118" s="11"/>
-      <c r="R118" s="11"/>
-      <c r="S118" s="11"/>
-      <c r="T118" s="11"/>
+      <c r="J118" s="10"/>
+      <c r="Q118" s="10"/>
+      <c r="R118" s="10"/>
+      <c r="S118" s="10"/>
+      <c r="T118" s="10"/>
     </row>
     <row r="119">
-      <c r="J119" s="11"/>
-      <c r="Q119" s="11"/>
-      <c r="R119" s="11"/>
-      <c r="S119" s="11"/>
-      <c r="T119" s="11"/>
+      <c r="J119" s="10"/>
+      <c r="Q119" s="10"/>
+      <c r="R119" s="10"/>
+      <c r="S119" s="10"/>
+      <c r="T119" s="10"/>
     </row>
     <row r="120">
-      <c r="J120" s="11"/>
-      <c r="Q120" s="11"/>
-      <c r="R120" s="11"/>
-      <c r="S120" s="11"/>
-      <c r="T120" s="11"/>
+      <c r="J120" s="10"/>
+      <c r="Q120" s="10"/>
+      <c r="R120" s="10"/>
+      <c r="S120" s="10"/>
+      <c r="T120" s="10"/>
     </row>
     <row r="121">
-      <c r="J121" s="11"/>
-      <c r="Q121" s="11"/>
-      <c r="R121" s="11"/>
-      <c r="S121" s="11"/>
-      <c r="T121" s="11"/>
+      <c r="J121" s="10"/>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
+      <c r="S121" s="10"/>
+      <c r="T121" s="10"/>
     </row>
     <row r="122">
-      <c r="J122" s="11"/>
-      <c r="Q122" s="11"/>
-      <c r="R122" s="11"/>
-      <c r="S122" s="11"/>
-      <c r="T122" s="11"/>
+      <c r="J122" s="10"/>
+      <c r="Q122" s="10"/>
+      <c r="R122" s="10"/>
+      <c r="S122" s="10"/>
+      <c r="T122" s="10"/>
     </row>
     <row r="123">
-      <c r="J123" s="11"/>
-      <c r="Q123" s="11"/>
-      <c r="R123" s="11"/>
-      <c r="S123" s="11"/>
-      <c r="T123" s="11"/>
+      <c r="J123" s="10"/>
+      <c r="Q123" s="10"/>
+      <c r="R123" s="10"/>
+      <c r="S123" s="10"/>
+      <c r="T123" s="10"/>
     </row>
     <row r="124">
-      <c r="J124" s="11"/>
-      <c r="Q124" s="11"/>
-      <c r="R124" s="11"/>
-      <c r="S124" s="11"/>
-      <c r="T124" s="11"/>
+      <c r="J124" s="10"/>
+      <c r="Q124" s="10"/>
+      <c r="R124" s="10"/>
+      <c r="S124" s="10"/>
+      <c r="T124" s="10"/>
     </row>
     <row r="125">
-      <c r="J125" s="11"/>
-      <c r="Q125" s="11"/>
-      <c r="R125" s="11"/>
-      <c r="S125" s="11"/>
-      <c r="T125" s="11"/>
+      <c r="J125" s="10"/>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="10"/>
+      <c r="S125" s="10"/>
+      <c r="T125" s="10"/>
     </row>
     <row r="126">
-      <c r="J126" s="11"/>
-      <c r="Q126" s="11"/>
-      <c r="R126" s="11"/>
-      <c r="S126" s="11"/>
-      <c r="T126" s="11"/>
+      <c r="J126" s="10"/>
+      <c r="Q126" s="10"/>
+      <c r="R126" s="10"/>
+      <c r="S126" s="10"/>
+      <c r="T126" s="10"/>
     </row>
     <row r="127">
-      <c r="J127" s="11"/>
-      <c r="Q127" s="11"/>
-      <c r="R127" s="11"/>
-      <c r="S127" s="11"/>
-      <c r="T127" s="11"/>
+      <c r="J127" s="10"/>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="10"/>
+      <c r="S127" s="10"/>
+      <c r="T127" s="10"/>
     </row>
     <row r="128">
-      <c r="J128" s="11"/>
-      <c r="Q128" s="11"/>
-      <c r="R128" s="11"/>
-      <c r="S128" s="11"/>
-      <c r="T128" s="11"/>
+      <c r="J128" s="10"/>
+      <c r="Q128" s="10"/>
+      <c r="R128" s="10"/>
+      <c r="S128" s="10"/>
+      <c r="T128" s="10"/>
     </row>
     <row r="129">
-      <c r="J129" s="11"/>
-      <c r="Q129" s="11"/>
-      <c r="R129" s="11"/>
-      <c r="S129" s="11"/>
-      <c r="T129" s="11"/>
+      <c r="J129" s="10"/>
+      <c r="Q129" s="10"/>
+      <c r="R129" s="10"/>
+      <c r="S129" s="10"/>
+      <c r="T129" s="10"/>
     </row>
     <row r="130">
-      <c r="J130" s="11"/>
-      <c r="Q130" s="11"/>
-      <c r="R130" s="11"/>
-      <c r="S130" s="11"/>
-      <c r="T130" s="11"/>
+      <c r="J130" s="10"/>
+      <c r="Q130" s="10"/>
+      <c r="R130" s="10"/>
+      <c r="S130" s="10"/>
+      <c r="T130" s="10"/>
     </row>
     <row r="131">
-      <c r="J131" s="11"/>
-      <c r="Q131" s="11"/>
-      <c r="R131" s="11"/>
-      <c r="S131" s="11"/>
-      <c r="T131" s="11"/>
+      <c r="J131" s="10"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
+      <c r="T131" s="10"/>
     </row>
     <row r="132">
-      <c r="J132" s="11"/>
-      <c r="Q132" s="11"/>
-      <c r="R132" s="11"/>
-      <c r="S132" s="11"/>
-      <c r="T132" s="11"/>
+      <c r="J132" s="10"/>
+      <c r="Q132" s="10"/>
+      <c r="R132" s="10"/>
+      <c r="S132" s="10"/>
+      <c r="T132" s="10"/>
     </row>
     <row r="133">
-      <c r="J133" s="11"/>
-      <c r="Q133" s="11"/>
-      <c r="R133" s="11"/>
-      <c r="S133" s="11"/>
-      <c r="T133" s="11"/>
+      <c r="J133" s="10"/>
+      <c r="Q133" s="10"/>
+      <c r="R133" s="10"/>
+      <c r="S133" s="10"/>
+      <c r="T133" s="10"/>
     </row>
     <row r="134">
-      <c r="J134" s="11"/>
-      <c r="Q134" s="11"/>
-      <c r="R134" s="11"/>
-      <c r="S134" s="11"/>
-      <c r="T134" s="11"/>
+      <c r="J134" s="10"/>
+      <c r="Q134" s="10"/>
+      <c r="R134" s="10"/>
+      <c r="S134" s="10"/>
+      <c r="T134" s="10"/>
     </row>
     <row r="135">
-      <c r="J135" s="11"/>
-      <c r="Q135" s="11"/>
-      <c r="R135" s="11"/>
-      <c r="S135" s="11"/>
-      <c r="T135" s="11"/>
+      <c r="J135" s="10"/>
+      <c r="Q135" s="10"/>
+      <c r="R135" s="10"/>
+      <c r="S135" s="10"/>
+      <c r="T135" s="10"/>
     </row>
     <row r="136">
-      <c r="J136" s="11"/>
-      <c r="Q136" s="11"/>
-      <c r="R136" s="11"/>
-      <c r="S136" s="11"/>
-      <c r="T136" s="11"/>
+      <c r="J136" s="10"/>
+      <c r="Q136" s="10"/>
+      <c r="R136" s="10"/>
+      <c r="S136" s="10"/>
+      <c r="T136" s="10"/>
     </row>
     <row r="137">
-      <c r="J137" s="11"/>
-      <c r="Q137" s="11"/>
-      <c r="R137" s="11"/>
-      <c r="S137" s="11"/>
-      <c r="T137" s="11"/>
+      <c r="J137" s="10"/>
+      <c r="Q137" s="10"/>
+      <c r="R137" s="10"/>
+      <c r="S137" s="10"/>
+      <c r="T137" s="10"/>
     </row>
     <row r="138">
-      <c r="J138" s="11"/>
-      <c r="Q138" s="11"/>
-      <c r="R138" s="11"/>
-      <c r="S138" s="11"/>
-      <c r="T138" s="11"/>
+      <c r="J138" s="10"/>
+      <c r="Q138" s="10"/>
+      <c r="R138" s="10"/>
+      <c r="S138" s="10"/>
+      <c r="T138" s="10"/>
     </row>
     <row r="139">
-      <c r="J139" s="11"/>
-      <c r="Q139" s="11"/>
-      <c r="R139" s="11"/>
-      <c r="S139" s="11"/>
-      <c r="T139" s="11"/>
+      <c r="J139" s="10"/>
+      <c r="Q139" s="10"/>
+      <c r="R139" s="10"/>
+      <c r="S139" s="10"/>
+      <c r="T139" s="10"/>
     </row>
     <row r="140">
-      <c r="J140" s="11"/>
-      <c r="Q140" s="11"/>
-      <c r="R140" s="11"/>
-      <c r="S140" s="11"/>
-      <c r="T140" s="11"/>
+      <c r="J140" s="10"/>
+      <c r="Q140" s="10"/>
+      <c r="R140" s="10"/>
+      <c r="S140" s="10"/>
+      <c r="T140" s="10"/>
     </row>
     <row r="141">
-      <c r="J141" s="11"/>
-      <c r="Q141" s="11"/>
-      <c r="R141" s="11"/>
-      <c r="S141" s="11"/>
-      <c r="T141" s="11"/>
+      <c r="J141" s="10"/>
+      <c r="Q141" s="10"/>
+      <c r="R141" s="10"/>
+      <c r="S141" s="10"/>
+      <c r="T141" s="10"/>
     </row>
     <row r="142">
-      <c r="J142" s="11"/>
-      <c r="Q142" s="11"/>
-      <c r="R142" s="11"/>
-      <c r="S142" s="11"/>
-      <c r="T142" s="11"/>
+      <c r="J142" s="10"/>
+      <c r="Q142" s="10"/>
+      <c r="R142" s="10"/>
+      <c r="S142" s="10"/>
+      <c r="T142" s="10"/>
     </row>
     <row r="143">
-      <c r="J143" s="11"/>
-      <c r="Q143" s="11"/>
-      <c r="R143" s="11"/>
-      <c r="S143" s="11"/>
-      <c r="T143" s="11"/>
+      <c r="J143" s="10"/>
+      <c r="Q143" s="10"/>
+      <c r="R143" s="10"/>
+      <c r="S143" s="10"/>
+      <c r="T143" s="10"/>
     </row>
     <row r="144">
-      <c r="J144" s="11"/>
-      <c r="Q144" s="11"/>
-      <c r="R144" s="11"/>
-      <c r="S144" s="11"/>
-      <c r="T144" s="11"/>
+      <c r="J144" s="10"/>
+      <c r="Q144" s="10"/>
+      <c r="R144" s="10"/>
+      <c r="S144" s="10"/>
+      <c r="T144" s="10"/>
     </row>
     <row r="145">
-      <c r="J145" s="11"/>
-      <c r="Q145" s="11"/>
-      <c r="R145" s="11"/>
-      <c r="S145" s="11"/>
-      <c r="T145" s="11"/>
+      <c r="J145" s="10"/>
+      <c r="Q145" s="10"/>
+      <c r="R145" s="10"/>
+      <c r="S145" s="10"/>
+      <c r="T145" s="10"/>
     </row>
     <row r="146">
-      <c r="J146" s="11"/>
-      <c r="Q146" s="11"/>
-      <c r="R146" s="11"/>
-      <c r="S146" s="11"/>
-      <c r="T146" s="11"/>
+      <c r="J146" s="10"/>
+      <c r="Q146" s="10"/>
+      <c r="R146" s="10"/>
+      <c r="S146" s="10"/>
+      <c r="T146" s="10"/>
     </row>
     <row r="147">
-      <c r="J147" s="11"/>
-      <c r="Q147" s="11"/>
-      <c r="R147" s="11"/>
-      <c r="S147" s="11"/>
-      <c r="T147" s="11"/>
+      <c r="J147" s="10"/>
+      <c r="Q147" s="10"/>
+      <c r="R147" s="10"/>
+      <c r="S147" s="10"/>
+      <c r="T147" s="10"/>
     </row>
     <row r="148">
-      <c r="J148" s="11"/>
-      <c r="Q148" s="11"/>
-      <c r="R148" s="11"/>
-      <c r="S148" s="11"/>
-      <c r="T148" s="11"/>
+      <c r="J148" s="10"/>
+      <c r="Q148" s="10"/>
+      <c r="R148" s="10"/>
+      <c r="S148" s="10"/>
+      <c r="T148" s="10"/>
     </row>
     <row r="149">
-      <c r="J149" s="11"/>
-      <c r="Q149" s="11"/>
-      <c r="R149" s="11"/>
-      <c r="S149" s="11"/>
-      <c r="T149" s="11"/>
+      <c r="J149" s="10"/>
+      <c r="Q149" s="10"/>
+      <c r="R149" s="10"/>
+      <c r="S149" s="10"/>
+      <c r="T149" s="10"/>
     </row>
     <row r="150">
-      <c r="J150" s="11"/>
-      <c r="Q150" s="11"/>
-      <c r="R150" s="11"/>
-      <c r="S150" s="11"/>
-      <c r="T150" s="11"/>
+      <c r="J150" s="10"/>
+      <c r="Q150" s="10"/>
+      <c r="R150" s="10"/>
+      <c r="S150" s="10"/>
+      <c r="T150" s="10"/>
     </row>
     <row r="151">
-      <c r="J151" s="11"/>
-      <c r="Q151" s="11"/>
-      <c r="R151" s="11"/>
-      <c r="S151" s="11"/>
-      <c r="T151" s="11"/>
+      <c r="J151" s="10"/>
+      <c r="Q151" s="10"/>
+      <c r="R151" s="10"/>
+      <c r="S151" s="10"/>
+      <c r="T151" s="10"/>
     </row>
     <row r="152">
-      <c r="J152" s="11"/>
-      <c r="Q152" s="11"/>
-      <c r="R152" s="11"/>
-      <c r="S152" s="11"/>
-      <c r="T152" s="11"/>
+      <c r="J152" s="10"/>
+      <c r="Q152" s="10"/>
+      <c r="R152" s="10"/>
+      <c r="S152" s="10"/>
+      <c r="T152" s="10"/>
     </row>
     <row r="153">
-      <c r="J153" s="11"/>
-      <c r="Q153" s="11"/>
-      <c r="R153" s="11"/>
-      <c r="S153" s="11"/>
-      <c r="T153" s="11"/>
+      <c r="J153" s="10"/>
+      <c r="Q153" s="10"/>
+      <c r="R153" s="10"/>
+      <c r="S153" s="10"/>
+      <c r="T153" s="10"/>
     </row>
     <row r="154">
-      <c r="J154" s="11"/>
-      <c r="Q154" s="11"/>
-      <c r="R154" s="11"/>
-      <c r="S154" s="11"/>
-      <c r="T154" s="11"/>
+      <c r="J154" s="10"/>
+      <c r="Q154" s="10"/>
+      <c r="R154" s="10"/>
+      <c r="S154" s="10"/>
+      <c r="T154" s="10"/>
     </row>
     <row r="155">
-      <c r="J155" s="11"/>
-      <c r="Q155" s="11"/>
-      <c r="R155" s="11"/>
-      <c r="S155" s="11"/>
-      <c r="T155" s="11"/>
+      <c r="J155" s="10"/>
+      <c r="Q155" s="10"/>
+      <c r="R155" s="10"/>
+      <c r="S155" s="10"/>
+      <c r="T155" s="10"/>
     </row>
     <row r="156">
-      <c r="J156" s="11"/>
-      <c r="Q156" s="11"/>
-      <c r="R156" s="11"/>
-      <c r="S156" s="11"/>
-      <c r="T156" s="11"/>
+      <c r="J156" s="10"/>
+      <c r="Q156" s="10"/>
+      <c r="R156" s="10"/>
+      <c r="S156" s="10"/>
+      <c r="T156" s="10"/>
     </row>
     <row r="157">
-      <c r="J157" s="11"/>
-      <c r="Q157" s="11"/>
-      <c r="R157" s="11"/>
-      <c r="S157" s="11"/>
-      <c r="T157" s="11"/>
+      <c r="J157" s="10"/>
+      <c r="Q157" s="10"/>
+      <c r="R157" s="10"/>
+      <c r="S157" s="10"/>
+      <c r="T157" s="10"/>
     </row>
     <row r="158">
-      <c r="J158" s="11"/>
-      <c r="Q158" s="11"/>
-      <c r="R158" s="11"/>
-      <c r="S158" s="11"/>
-      <c r="T158" s="11"/>
+      <c r="J158" s="10"/>
+      <c r="Q158" s="10"/>
+      <c r="R158" s="10"/>
+      <c r="S158" s="10"/>
+      <c r="T158" s="10"/>
     </row>
     <row r="159">
-      <c r="J159" s="11"/>
-      <c r="Q159" s="11"/>
-      <c r="R159" s="11"/>
-      <c r="S159" s="11"/>
-      <c r="T159" s="11"/>
+      <c r="J159" s="10"/>
+      <c r="Q159" s="10"/>
+      <c r="R159" s="10"/>
+      <c r="S159" s="10"/>
+      <c r="T159" s="10"/>
     </row>
     <row r="160">
-      <c r="J160" s="11"/>
-      <c r="Q160" s="11"/>
-      <c r="R160" s="11"/>
-      <c r="S160" s="11"/>
-      <c r="T160" s="11"/>
+      <c r="J160" s="10"/>
+      <c r="Q160" s="10"/>
+      <c r="R160" s="10"/>
+      <c r="S160" s="10"/>
+      <c r="T160" s="10"/>
     </row>
     <row r="161">
-      <c r="J161" s="11"/>
-      <c r="Q161" s="11"/>
-      <c r="R161" s="11"/>
-      <c r="S161" s="11"/>
-      <c r="T161" s="11"/>
+      <c r="J161" s="10"/>
+      <c r="Q161" s="10"/>
+      <c r="R161" s="10"/>
+      <c r="S161" s="10"/>
+      <c r="T161" s="10"/>
     </row>
     <row r="162">
-      <c r="J162" s="11"/>
-      <c r="Q162" s="11"/>
-      <c r="R162" s="11"/>
-      <c r="S162" s="11"/>
-      <c r="T162" s="11"/>
+      <c r="J162" s="10"/>
+      <c r="Q162" s="10"/>
+      <c r="R162" s="10"/>
+      <c r="S162" s="10"/>
+      <c r="T162" s="10"/>
     </row>
     <row r="163">
-      <c r="J163" s="11"/>
-      <c r="Q163" s="11"/>
-      <c r="R163" s="11"/>
-      <c r="S163" s="11"/>
-      <c r="T163" s="11"/>
+      <c r="J163" s="10"/>
+      <c r="Q163" s="10"/>
+      <c r="R163" s="10"/>
+      <c r="S163" s="10"/>
+      <c r="T163" s="10"/>
     </row>
     <row r="164">
-      <c r="J164" s="11"/>
-      <c r="Q164" s="11"/>
-      <c r="R164" s="11"/>
-      <c r="S164" s="11"/>
-      <c r="T164" s="11"/>
+      <c r="J164" s="10"/>
+      <c r="Q164" s="10"/>
+      <c r="R164" s="10"/>
+      <c r="S164" s="10"/>
+      <c r="T164" s="10"/>
     </row>
     <row r="165">
-      <c r="J165" s="11"/>
-      <c r="Q165" s="11"/>
-      <c r="R165" s="11"/>
-      <c r="S165" s="11"/>
-      <c r="T165" s="11"/>
+      <c r="J165" s="10"/>
+      <c r="Q165" s="10"/>
+      <c r="R165" s="10"/>
+      <c r="S165" s="10"/>
+      <c r="T165" s="10"/>
     </row>
     <row r="166">
-      <c r="J166" s="11"/>
-      <c r="Q166" s="11"/>
-      <c r="R166" s="11"/>
-      <c r="S166" s="11"/>
-      <c r="T166" s="11"/>
+      <c r="J166" s="10"/>
+      <c r="Q166" s="10"/>
+      <c r="R166" s="10"/>
+      <c r="S166" s="10"/>
+      <c r="T166" s="10"/>
     </row>
     <row r="167">
-      <c r="J167" s="11"/>
-      <c r="Q167" s="11"/>
-      <c r="R167" s="11"/>
-      <c r="S167" s="11"/>
-      <c r="T167" s="11"/>
+      <c r="J167" s="10"/>
+      <c r="Q167" s="10"/>
+      <c r="R167" s="10"/>
+      <c r="S167" s="10"/>
+      <c r="T167" s="10"/>
     </row>
     <row r="168">
-      <c r="J168" s="11"/>
-      <c r="Q168" s="11"/>
-      <c r="R168" s="11"/>
-      <c r="S168" s="11"/>
-      <c r="T168" s="11"/>
+      <c r="J168" s="10"/>
+      <c r="Q168" s="10"/>
+      <c r="R168" s="10"/>
+      <c r="S168" s="10"/>
+      <c r="T168" s="10"/>
     </row>
     <row r="169">
-      <c r="J169" s="11"/>
-      <c r="Q169" s="11"/>
-      <c r="R169" s="11"/>
-      <c r="S169" s="11"/>
-      <c r="T169" s="11"/>
+      <c r="J169" s="10"/>
+      <c r="Q169" s="10"/>
+      <c r="R169" s="10"/>
+      <c r="S169" s="10"/>
+      <c r="T169" s="10"/>
     </row>
     <row r="170">
-      <c r="J170" s="11"/>
-      <c r="Q170" s="11"/>
-      <c r="R170" s="11"/>
-      <c r="S170" s="11"/>
-      <c r="T170" s="11"/>
+      <c r="J170" s="10"/>
+      <c r="Q170" s="10"/>
+      <c r="R170" s="10"/>
+      <c r="S170" s="10"/>
+      <c r="T170" s="10"/>
     </row>
     <row r="171">
-      <c r="J171" s="11"/>
-      <c r="Q171" s="11"/>
-      <c r="R171" s="11"/>
-      <c r="S171" s="11"/>
-      <c r="T171" s="11"/>
+      <c r="J171" s="10"/>
+      <c r="Q171" s="10"/>
+      <c r="R171" s="10"/>
+      <c r="S171" s="10"/>
+      <c r="T171" s="10"/>
     </row>
     <row r="172">
-      <c r="J172" s="11"/>
-      <c r="Q172" s="11"/>
-      <c r="R172" s="11"/>
-      <c r="S172" s="11"/>
-      <c r="T172" s="11"/>
+      <c r="J172" s="10"/>
+      <c r="Q172" s="10"/>
+      <c r="R172" s="10"/>
+      <c r="S172" s="10"/>
+      <c r="T172" s="10"/>
     </row>
     <row r="173">
-      <c r="J173" s="11"/>
-      <c r="Q173" s="11"/>
-      <c r="R173" s="11"/>
-      <c r="S173" s="11"/>
-      <c r="T173" s="11"/>
+      <c r="J173" s="10"/>
+      <c r="Q173" s="10"/>
+      <c r="R173" s="10"/>
+      <c r="S173" s="10"/>
+      <c r="T173" s="10"/>
     </row>
     <row r="174">
-      <c r="J174" s="11"/>
-      <c r="Q174" s="11"/>
-      <c r="R174" s="11"/>
-      <c r="S174" s="11"/>
-      <c r="T174" s="11"/>
+      <c r="J174" s="10"/>
+      <c r="Q174" s="10"/>
+      <c r="R174" s="10"/>
+      <c r="S174" s="10"/>
+      <c r="T174" s="10"/>
     </row>
     <row r="175">
-      <c r="J175" s="11"/>
-      <c r="Q175" s="11"/>
-      <c r="R175" s="11"/>
-      <c r="S175" s="11"/>
-      <c r="T175" s="11"/>
+      <c r="J175" s="10"/>
+      <c r="Q175" s="10"/>
+      <c r="R175" s="10"/>
+      <c r="S175" s="10"/>
+      <c r="T175" s="10"/>
     </row>
     <row r="176">
-      <c r="J176" s="11"/>
-      <c r="Q176" s="11"/>
-      <c r="R176" s="11"/>
-      <c r="S176" s="11"/>
-      <c r="T176" s="11"/>
+      <c r="J176" s="10"/>
+      <c r="Q176" s="10"/>
+      <c r="R176" s="10"/>
+      <c r="S176" s="10"/>
+      <c r="T176" s="10"/>
     </row>
     <row r="177">
-      <c r="J177" s="11"/>
-      <c r="Q177" s="11"/>
-      <c r="R177" s="11"/>
-      <c r="S177" s="11"/>
-      <c r="T177" s="11"/>
+      <c r="J177" s="10"/>
+      <c r="Q177" s="10"/>
+      <c r="R177" s="10"/>
+      <c r="S177" s="10"/>
+      <c r="T177" s="10"/>
     </row>
     <row r="178">
-      <c r="J178" s="11"/>
-      <c r="Q178" s="11"/>
-      <c r="R178" s="11"/>
-      <c r="S178" s="11"/>
-      <c r="T178" s="11"/>
+      <c r="J178" s="10"/>
+      <c r="Q178" s="10"/>
+      <c r="R178" s="10"/>
+      <c r="S178" s="10"/>
+      <c r="T178" s="10"/>
     </row>
     <row r="179">
-      <c r="J179" s="11"/>
-      <c r="Q179" s="11"/>
-      <c r="R179" s="11"/>
-      <c r="S179" s="11"/>
-      <c r="T179" s="11"/>
+      <c r="J179" s="10"/>
+      <c r="Q179" s="10"/>
+      <c r="R179" s="10"/>
+      <c r="S179" s="10"/>
+      <c r="T179" s="10"/>
     </row>
     <row r="180">
-      <c r="J180" s="11"/>
-      <c r="Q180" s="11"/>
-      <c r="R180" s="11"/>
-      <c r="S180" s="11"/>
-      <c r="T180" s="11"/>
+      <c r="J180" s="10"/>
+      <c r="Q180" s="10"/>
+      <c r="R180" s="10"/>
+      <c r="S180" s="10"/>
+      <c r="T180" s="10"/>
     </row>
     <row r="181">
-      <c r="J181" s="11"/>
-      <c r="Q181" s="11"/>
-      <c r="R181" s="11"/>
-      <c r="S181" s="11"/>
-      <c r="T181" s="11"/>
+      <c r="J181" s="10"/>
+      <c r="Q181" s="10"/>
+      <c r="R181" s="10"/>
+      <c r="S181" s="10"/>
+      <c r="T181" s="10"/>
     </row>
     <row r="182">
-      <c r="J182" s="11"/>
-      <c r="Q182" s="11"/>
-      <c r="R182" s="11"/>
-      <c r="S182" s="11"/>
-      <c r="T182" s="11"/>
+      <c r="J182" s="10"/>
+      <c r="Q182" s="10"/>
+      <c r="R182" s="10"/>
+      <c r="S182" s="10"/>
+      <c r="T182" s="10"/>
     </row>
     <row r="183">
-      <c r="J183" s="11"/>
-      <c r="Q183" s="11"/>
-      <c r="R183" s="11"/>
-      <c r="S183" s="11"/>
-      <c r="T183" s="11"/>
+      <c r="J183" s="10"/>
+      <c r="Q183" s="10"/>
+      <c r="R183" s="10"/>
+      <c r="S183" s="10"/>
+      <c r="T183" s="10"/>
     </row>
     <row r="184">
-      <c r="J184" s="11"/>
-      <c r="Q184" s="11"/>
-      <c r="R184" s="11"/>
-      <c r="S184" s="11"/>
-      <c r="T184" s="11"/>
+      <c r="J184" s="10"/>
+      <c r="Q184" s="10"/>
+      <c r="R184" s="10"/>
+      <c r="S184" s="10"/>
+      <c r="T184" s="10"/>
     </row>
     <row r="185">
-      <c r="J185" s="11"/>
-      <c r="Q185" s="11"/>
-      <c r="R185" s="11"/>
-      <c r="S185" s="11"/>
-      <c r="T185" s="11"/>
+      <c r="J185" s="10"/>
+      <c r="Q185" s="10"/>
+      <c r="R185" s="10"/>
+      <c r="S185" s="10"/>
+      <c r="T185" s="10"/>
     </row>
     <row r="186">
-      <c r="J186" s="11"/>
-      <c r="Q186" s="11"/>
-      <c r="R186" s="11"/>
-      <c r="S186" s="11"/>
-      <c r="T186" s="11"/>
+      <c r="J186" s="10"/>
+      <c r="Q186" s="10"/>
+      <c r="R186" s="10"/>
+      <c r="S186" s="10"/>
+      <c r="T186" s="10"/>
     </row>
     <row r="187">
-      <c r="J187" s="11"/>
-      <c r="Q187" s="11"/>
-      <c r="R187" s="11"/>
-      <c r="S187" s="11"/>
-      <c r="T187" s="11"/>
+      <c r="J187" s="10"/>
+      <c r="Q187" s="10"/>
+      <c r="R187" s="10"/>
+      <c r="S187" s="10"/>
+      <c r="T187" s="10"/>
     </row>
     <row r="188">
-      <c r="J188" s="11"/>
-      <c r="Q188" s="11"/>
-      <c r="R188" s="11"/>
-      <c r="S188" s="11"/>
-      <c r="T188" s="11"/>
+      <c r="J188" s="10"/>
+      <c r="Q188" s="10"/>
+      <c r="R188" s="10"/>
+      <c r="S188" s="10"/>
+      <c r="T188" s="10"/>
     </row>
     <row r="189">
-      <c r="J189" s="11"/>
-      <c r="Q189" s="11"/>
-      <c r="R189" s="11"/>
-      <c r="S189" s="11"/>
-      <c r="T189" s="11"/>
+      <c r="J189" s="10"/>
+      <c r="Q189" s="10"/>
+      <c r="R189" s="10"/>
+      <c r="S189" s="10"/>
+      <c r="T189" s="10"/>
     </row>
     <row r="190">
-      <c r="J190" s="11"/>
-      <c r="Q190" s="11"/>
-      <c r="R190" s="11"/>
-      <c r="S190" s="11"/>
-      <c r="T190" s="11"/>
+      <c r="J190" s="10"/>
+      <c r="Q190" s="10"/>
+      <c r="R190" s="10"/>
+      <c r="S190" s="10"/>
+      <c r="T190" s="10"/>
     </row>
     <row r="191">
-      <c r="J191" s="11"/>
-      <c r="Q191" s="11"/>
-      <c r="R191" s="11"/>
-      <c r="S191" s="11"/>
-      <c r="T191" s="11"/>
+      <c r="J191" s="10"/>
+      <c r="Q191" s="10"/>
+      <c r="R191" s="10"/>
+      <c r="S191" s="10"/>
+      <c r="T191" s="10"/>
     </row>
     <row r="192">
-      <c r="J192" s="11"/>
-      <c r="Q192" s="11"/>
-      <c r="R192" s="11"/>
-      <c r="S192" s="11"/>
-      <c r="T192" s="11"/>
+      <c r="J192" s="10"/>
+      <c r="Q192" s="10"/>
+      <c r="R192" s="10"/>
+      <c r="S192" s="10"/>
+      <c r="T192" s="10"/>
     </row>
     <row r="193">
-      <c r="J193" s="11"/>
-      <c r="Q193" s="11"/>
-      <c r="R193" s="11"/>
-      <c r="S193" s="11"/>
-      <c r="T193" s="11"/>
+      <c r="J193" s="10"/>
+      <c r="Q193" s="10"/>
+      <c r="R193" s="10"/>
+      <c r="S193" s="10"/>
+      <c r="T193" s="10"/>
     </row>
     <row r="194">
-      <c r="J194" s="11"/>
-      <c r="Q194" s="11"/>
-      <c r="R194" s="11"/>
-      <c r="S194" s="11"/>
-      <c r="T194" s="11"/>
+      <c r="J194" s="10"/>
+      <c r="Q194" s="10"/>
+      <c r="R194" s="10"/>
+      <c r="S194" s="10"/>
+      <c r="T194" s="10"/>
     </row>
     <row r="195">
-      <c r="J195" s="11"/>
-      <c r="Q195" s="11"/>
-      <c r="R195" s="11"/>
-      <c r="S195" s="11"/>
-      <c r="T195" s="11"/>
+      <c r="J195" s="10"/>
+      <c r="Q195" s="10"/>
+      <c r="R195" s="10"/>
+      <c r="S195" s="10"/>
+      <c r="T195" s="10"/>
     </row>
     <row r="196">
-      <c r="J196" s="11"/>
-      <c r="Q196" s="11"/>
-      <c r="R196" s="11"/>
-      <c r="S196" s="11"/>
-      <c r="T196" s="11"/>
+      <c r="J196" s="10"/>
+      <c r="Q196" s="10"/>
+      <c r="R196" s="10"/>
+      <c r="S196" s="10"/>
+      <c r="T196" s="10"/>
     </row>
     <row r="197">
-      <c r="J197" s="11"/>
-      <c r="Q197" s="11"/>
-      <c r="R197" s="11"/>
-      <c r="S197" s="11"/>
-      <c r="T197" s="11"/>
+      <c r="J197" s="10"/>
+      <c r="Q197" s="10"/>
+      <c r="R197" s="10"/>
+      <c r="S197" s="10"/>
+      <c r="T197" s="10"/>
     </row>
     <row r="198">
-      <c r="J198" s="11"/>
-      <c r="Q198" s="11"/>
-      <c r="R198" s="11"/>
-      <c r="S198" s="11"/>
-      <c r="T198" s="11"/>
+      <c r="J198" s="10"/>
+      <c r="Q198" s="10"/>
+      <c r="R198" s="10"/>
+      <c r="S198" s="10"/>
+      <c r="T198" s="10"/>
     </row>
     <row r="199">
-      <c r="J199" s="11"/>
-      <c r="Q199" s="11"/>
-      <c r="R199" s="11"/>
-      <c r="S199" s="11"/>
-      <c r="T199" s="11"/>
+      <c r="J199" s="10"/>
+      <c r="Q199" s="10"/>
+      <c r="R199" s="10"/>
+      <c r="S199" s="10"/>
+      <c r="T199" s="10"/>
     </row>
     <row r="200">
-      <c r="J200" s="11"/>
-      <c r="Q200" s="11"/>
-      <c r="R200" s="11"/>
-      <c r="S200" s="11"/>
-      <c r="T200" s="11"/>
+      <c r="J200" s="10"/>
+      <c r="Q200" s="10"/>
+      <c r="R200" s="10"/>
+      <c r="S200" s="10"/>
+      <c r="T200" s="10"/>
     </row>
     <row r="201">
-      <c r="J201" s="11"/>
-      <c r="Q201" s="11"/>
-      <c r="R201" s="11"/>
-      <c r="S201" s="11"/>
-      <c r="T201" s="11"/>
+      <c r="J201" s="10"/>
+      <c r="Q201" s="10"/>
+      <c r="R201" s="10"/>
+      <c r="S201" s="10"/>
+      <c r="T201" s="10"/>
     </row>
     <row r="202">
-      <c r="J202" s="11"/>
-      <c r="Q202" s="11"/>
-      <c r="R202" s="11"/>
-      <c r="S202" s="11"/>
-      <c r="T202" s="11"/>
+      <c r="J202" s="10"/>
+      <c r="Q202" s="10"/>
+      <c r="R202" s="10"/>
+      <c r="S202" s="10"/>
+      <c r="T202" s="10"/>
     </row>
     <row r="203">
-      <c r="J203" s="11"/>
-      <c r="Q203" s="11"/>
-      <c r="R203" s="11"/>
-      <c r="S203" s="11"/>
-      <c r="T203" s="11"/>
+      <c r="J203" s="10"/>
+      <c r="Q203" s="10"/>
+      <c r="R203" s="10"/>
+      <c r="S203" s="10"/>
+      <c r="T203" s="10"/>
     </row>
     <row r="204">
-      <c r="J204" s="11"/>
-      <c r="Q204" s="11"/>
-      <c r="R204" s="11"/>
-      <c r="S204" s="11"/>
-      <c r="T204" s="11"/>
+      <c r="J204" s="10"/>
+      <c r="Q204" s="10"/>
+      <c r="R204" s="10"/>
+      <c r="S204" s="10"/>
+      <c r="T204" s="10"/>
     </row>
     <row r="205">
-      <c r="J205" s="11"/>
-      <c r="Q205" s="11"/>
-      <c r="R205" s="11"/>
-      <c r="S205" s="11"/>
-      <c r="T205" s="11"/>
+      <c r="J205" s="10"/>
+      <c r="Q205" s="10"/>
+      <c r="R205" s="10"/>
+      <c r="S205" s="10"/>
+      <c r="T205" s="10"/>
     </row>
     <row r="206">
-      <c r="J206" s="11"/>
-      <c r="Q206" s="11"/>
-      <c r="R206" s="11"/>
-      <c r="S206" s="11"/>
-      <c r="T206" s="11"/>
+      <c r="J206" s="10"/>
+      <c r="Q206" s="10"/>
+      <c r="R206" s="10"/>
+      <c r="S206" s="10"/>
+      <c r="T206" s="10"/>
     </row>
     <row r="207">
-      <c r="J207" s="11"/>
-      <c r="Q207" s="11"/>
-      <c r="R207" s="11"/>
-      <c r="S207" s="11"/>
-      <c r="T207" s="11"/>
+      <c r="J207" s="10"/>
+      <c r="Q207" s="10"/>
+      <c r="R207" s="10"/>
+      <c r="S207" s="10"/>
+      <c r="T207" s="10"/>
     </row>
     <row r="208">
-      <c r="J208" s="11"/>
-      <c r="Q208" s="11"/>
-      <c r="R208" s="11"/>
-      <c r="S208" s="11"/>
-      <c r="T208" s="11"/>
+      <c r="J208" s="10"/>
+      <c r="Q208" s="10"/>
+      <c r="R208" s="10"/>
+      <c r="S208" s="10"/>
+      <c r="T208" s="10"/>
     </row>
     <row r="209">
-      <c r="J209" s="11"/>
-      <c r="Q209" s="11"/>
-      <c r="R209" s="11"/>
-      <c r="S209" s="11"/>
-      <c r="T209" s="11"/>
+      <c r="J209" s="10"/>
+      <c r="Q209" s="10"/>
+      <c r="R209" s="10"/>
+      <c r="S209" s="10"/>
+      <c r="T209" s="10"/>
     </row>
     <row r="210">
-      <c r="J210" s="11"/>
-      <c r="Q210" s="11"/>
-      <c r="R210" s="11"/>
-      <c r="S210" s="11"/>
-      <c r="T210" s="11"/>
+      <c r="J210" s="10"/>
+      <c r="Q210" s="10"/>
+      <c r="R210" s="10"/>
+      <c r="S210" s="10"/>
+      <c r="T210" s="10"/>
     </row>
     <row r="211">
-      <c r="J211" s="11"/>
-      <c r="Q211" s="11"/>
-      <c r="R211" s="11"/>
-      <c r="S211" s="11"/>
-      <c r="T211" s="11"/>
+      <c r="J211" s="10"/>
+      <c r="Q211" s="10"/>
+      <c r="R211" s="10"/>
+      <c r="S211" s="10"/>
+      <c r="T211" s="10"/>
     </row>
     <row r="212">
-      <c r="J212" s="11"/>
-      <c r="Q212" s="11"/>
-      <c r="R212" s="11"/>
-      <c r="S212" s="11"/>
-      <c r="T212" s="11"/>
+      <c r="J212" s="10"/>
+      <c r="Q212" s="10"/>
+      <c r="R212" s="10"/>
+      <c r="S212" s="10"/>
+      <c r="T212" s="10"/>
     </row>
     <row r="213">
-      <c r="J213" s="11"/>
-      <c r="Q213" s="11"/>
-      <c r="R213" s="11"/>
-      <c r="S213" s="11"/>
-      <c r="T213" s="11"/>
+      <c r="J213" s="10"/>
+      <c r="Q213" s="10"/>
+      <c r="R213" s="10"/>
+      <c r="S213" s="10"/>
+      <c r="T213" s="10"/>
     </row>
     <row r="214">
-      <c r="J214" s="11"/>
-      <c r="Q214" s="11"/>
-      <c r="R214" s="11"/>
-      <c r="S214" s="11"/>
-      <c r="T214" s="11"/>
+      <c r="J214" s="10"/>
+      <c r="Q214" s="10"/>
+      <c r="R214" s="10"/>
+      <c r="S214" s="10"/>
+      <c r="T214" s="10"/>
     </row>
     <row r="215">
-      <c r="J215" s="11"/>
-      <c r="Q215" s="11"/>
-      <c r="R215" s="11"/>
-      <c r="S215" s="11"/>
-      <c r="T215" s="11"/>
+      <c r="J215" s="10"/>
+      <c r="Q215" s="10"/>
+      <c r="R215" s="10"/>
+      <c r="S215" s="10"/>
+      <c r="T215" s="10"/>
     </row>
     <row r="216">
-      <c r="J216" s="11"/>
-      <c r="Q216" s="11"/>
-      <c r="R216" s="11"/>
-      <c r="S216" s="11"/>
-      <c r="T216" s="11"/>
+      <c r="J216" s="10"/>
+      <c r="Q216" s="10"/>
+      <c r="R216" s="10"/>
+      <c r="S216" s="10"/>
+      <c r="T216" s="10"/>
     </row>
     <row r="217">
-      <c r="J217" s="11"/>
-      <c r="Q217" s="11"/>
-      <c r="R217" s="11"/>
-      <c r="S217" s="11"/>
-      <c r="T217" s="11"/>
+      <c r="J217" s="10"/>
+      <c r="Q217" s="10"/>
+      <c r="R217" s="10"/>
+      <c r="S217" s="10"/>
+      <c r="T217" s="10"/>
     </row>
     <row r="218">
-      <c r="J218" s="11"/>
-      <c r="Q218" s="11"/>
-      <c r="R218" s="11"/>
-      <c r="S218" s="11"/>
-      <c r="T218" s="11"/>
+      <c r="J218" s="10"/>
+      <c r="Q218" s="10"/>
+      <c r="R218" s="10"/>
+      <c r="S218" s="10"/>
+      <c r="T218" s="10"/>
     </row>
     <row r="219">
-      <c r="J219" s="11"/>
-      <c r="Q219" s="11"/>
-      <c r="R219" s="11"/>
-      <c r="S219" s="11"/>
-      <c r="T219" s="11"/>
+      <c r="J219" s="10"/>
+      <c r="Q219" s="10"/>
+      <c r="R219" s="10"/>
+      <c r="S219" s="10"/>
+      <c r="T219" s="10"/>
     </row>
     <row r="220">
-      <c r="J220" s="11"/>
-      <c r="Q220" s="11"/>
-      <c r="R220" s="11"/>
-      <c r="S220" s="11"/>
-      <c r="T220" s="11"/>
+      <c r="J220" s="10"/>
+      <c r="Q220" s="10"/>
+      <c r="R220" s="10"/>
+      <c r="S220" s="10"/>
+      <c r="T220" s="10"/>
     </row>
     <row r="221">
-      <c r="J221" s="11"/>
-      <c r="Q221" s="11"/>
-      <c r="R221" s="11"/>
-      <c r="S221" s="11"/>
-      <c r="T221" s="11"/>
+      <c r="J221" s="10"/>
+      <c r="Q221" s="10"/>
+      <c r="R221" s="10"/>
+      <c r="S221" s="10"/>
+      <c r="T221" s="10"/>
     </row>
     <row r="222">
-      <c r="J222" s="11"/>
-      <c r="Q222" s="11"/>
-      <c r="R222" s="11"/>
-      <c r="S222" s="11"/>
-      <c r="T222" s="11"/>
+      <c r="J222" s="10"/>
+      <c r="Q222" s="10"/>
+      <c r="R222" s="10"/>
+      <c r="S222" s="10"/>
+      <c r="T222" s="10"/>
     </row>
     <row r="223">
-      <c r="J223" s="11"/>
-      <c r="Q223" s="11"/>
-      <c r="R223" s="11"/>
-      <c r="S223" s="11"/>
-      <c r="T223" s="11"/>
+      <c r="J223" s="10"/>
+      <c r="Q223" s="10"/>
+      <c r="R223" s="10"/>
+      <c r="S223" s="10"/>
+      <c r="T223" s="10"/>
     </row>
     <row r="224">
-      <c r="J224" s="11"/>
-      <c r="Q224" s="11"/>
-      <c r="R224" s="11"/>
-      <c r="S224" s="11"/>
-      <c r="T224" s="11"/>
+      <c r="J224" s="10"/>
+      <c r="Q224" s="10"/>
+      <c r="R224" s="10"/>
+      <c r="S224" s="10"/>
+      <c r="T224" s="10"/>
     </row>
     <row r="225">
-      <c r="J225" s="11"/>
-      <c r="Q225" s="11"/>
-      <c r="R225" s="11"/>
-      <c r="S225" s="11"/>
-      <c r="T225" s="11"/>
+      <c r="J225" s="10"/>
+      <c r="Q225" s="10"/>
+      <c r="R225" s="10"/>
+      <c r="S225" s="10"/>
+      <c r="T225" s="10"/>
     </row>
     <row r="226">
-      <c r="J226" s="11"/>
-      <c r="Q226" s="11"/>
-      <c r="R226" s="11"/>
-      <c r="S226" s="11"/>
-      <c r="T226" s="11"/>
+      <c r="J226" s="10"/>
+      <c r="Q226" s="10"/>
+      <c r="R226" s="10"/>
+      <c r="S226" s="10"/>
+      <c r="T226" s="10"/>
     </row>
     <row r="227">
-      <c r="J227" s="11"/>
-      <c r="Q227" s="11"/>
-      <c r="R227" s="11"/>
-      <c r="S227" s="11"/>
-      <c r="T227" s="11"/>
+      <c r="J227" s="10"/>
+      <c r="Q227" s="10"/>
+      <c r="R227" s="10"/>
+      <c r="S227" s="10"/>
+      <c r="T227" s="10"/>
     </row>
     <row r="228">
-      <c r="J228" s="11"/>
-      <c r="Q228" s="11"/>
-      <c r="R228" s="11"/>
-      <c r="S228" s="11"/>
-      <c r="T228" s="11"/>
+      <c r="J228" s="10"/>
+      <c r="Q228" s="10"/>
+      <c r="R228" s="10"/>
+      <c r="S228" s="10"/>
+      <c r="T228" s="10"/>
     </row>
     <row r="229">
-      <c r="J229" s="11"/>
-      <c r="Q229" s="11"/>
-      <c r="R229" s="11"/>
-      <c r="S229" s="11"/>
-      <c r="T229" s="11"/>
+      <c r="J229" s="10"/>
+      <c r="Q229" s="10"/>
+      <c r="R229" s="10"/>
+      <c r="S229" s="10"/>
+      <c r="T229" s="10"/>
     </row>
     <row r="230">
-      <c r="J230" s="11"/>
-      <c r="Q230" s="11"/>
-      <c r="R230" s="11"/>
-      <c r="S230" s="11"/>
-      <c r="T230" s="11"/>
+      <c r="J230" s="10"/>
+      <c r="Q230" s="10"/>
+      <c r="R230" s="10"/>
+      <c r="S230" s="10"/>
+      <c r="T230" s="10"/>
     </row>
     <row r="231">
-      <c r="J231" s="11"/>
-      <c r="Q231" s="11"/>
-      <c r="R231" s="11"/>
-      <c r="S231" s="11"/>
-      <c r="T231" s="11"/>
+      <c r="J231" s="10"/>
+      <c r="Q231" s="10"/>
+      <c r="R231" s="10"/>
+      <c r="S231" s="10"/>
+      <c r="T231" s="10"/>
     </row>
     <row r="232">
-      <c r="J232" s="11"/>
-      <c r="Q232" s="11"/>
-      <c r="R232" s="11"/>
-      <c r="S232" s="11"/>
-      <c r="T232" s="11"/>
+      <c r="J232" s="10"/>
+      <c r="Q232" s="10"/>
+      <c r="R232" s="10"/>
+      <c r="S232" s="10"/>
+      <c r="T232" s="10"/>
     </row>
     <row r="233">
-      <c r="J233" s="11"/>
-      <c r="Q233" s="11"/>
-      <c r="R233" s="11"/>
-      <c r="S233" s="11"/>
-      <c r="T233" s="11"/>
+      <c r="J233" s="10"/>
+      <c r="Q233" s="10"/>
+      <c r="R233" s="10"/>
+      <c r="S233" s="10"/>
+      <c r="T233" s="10"/>
     </row>
     <row r="234">
-      <c r="J234" s="11"/>
-      <c r="Q234" s="11"/>
-      <c r="R234" s="11"/>
-      <c r="S234" s="11"/>
-      <c r="T234" s="11"/>
+      <c r="J234" s="10"/>
+      <c r="Q234" s="10"/>
+      <c r="R234" s="10"/>
+      <c r="S234" s="10"/>
+      <c r="T234" s="10"/>
     </row>
     <row r="235">
-      <c r="J235" s="11"/>
-      <c r="Q235" s="11"/>
-      <c r="R235" s="11"/>
-      <c r="S235" s="11"/>
-      <c r="T235" s="11"/>
+      <c r="J235" s="10"/>
+      <c r="Q235" s="10"/>
+      <c r="R235" s="10"/>
+      <c r="S235" s="10"/>
+      <c r="T235" s="10"/>
     </row>
     <row r="236">
-      <c r="J236" s="11"/>
-      <c r="Q236" s="11"/>
-      <c r="R236" s="11"/>
-      <c r="S236" s="11"/>
-      <c r="T236" s="11"/>
+      <c r="J236" s="10"/>
+      <c r="Q236" s="10"/>
+      <c r="R236" s="10"/>
+      <c r="S236" s="10"/>
+      <c r="T236" s="10"/>
     </row>
     <row r="237">
-      <c r="J237" s="11"/>
-      <c r="Q237" s="11"/>
-      <c r="R237" s="11"/>
-      <c r="S237" s="11"/>
-      <c r="T237" s="11"/>
+      <c r="J237" s="10"/>
+      <c r="Q237" s="10"/>
+      <c r="R237" s="10"/>
+      <c r="S237" s="10"/>
+      <c r="T237" s="10"/>
     </row>
     <row r="238">
-      <c r="J238" s="11"/>
-      <c r="Q238" s="11"/>
-      <c r="R238" s="11"/>
-      <c r="S238" s="11"/>
-      <c r="T238" s="11"/>
+      <c r="J238" s="10"/>
+      <c r="Q238" s="10"/>
+      <c r="R238" s="10"/>
+      <c r="S238" s="10"/>
+      <c r="T238" s="10"/>
     </row>
     <row r="239">
-      <c r="J239" s="11"/>
-      <c r="Q239" s="11"/>
-      <c r="R239" s="11"/>
-      <c r="S239" s="11"/>
-      <c r="T239" s="11"/>
+      <c r="J239" s="10"/>
+      <c r="Q239" s="10"/>
+      <c r="R239" s="10"/>
+      <c r="S239" s="10"/>
+      <c r="T239" s="10"/>
     </row>
     <row r="240">
-      <c r="J240" s="11"/>
-      <c r="Q240" s="11"/>
-      <c r="R240" s="11"/>
-      <c r="S240" s="11"/>
-      <c r="T240" s="11"/>
+      <c r="J240" s="10"/>
+      <c r="Q240" s="10"/>
+      <c r="R240" s="10"/>
+      <c r="S240" s="10"/>
+      <c r="T240" s="10"/>
     </row>
     <row r="241">
-      <c r="J241" s="11"/>
-      <c r="Q241" s="11"/>
-      <c r="R241" s="11"/>
-      <c r="S241" s="11"/>
-      <c r="T241" s="11"/>
+      <c r="J241" s="10"/>
+      <c r="Q241" s="10"/>
+      <c r="R241" s="10"/>
+      <c r="S241" s="10"/>
+      <c r="T241" s="10"/>
     </row>
     <row r="242">
-      <c r="J242" s="11"/>
-      <c r="Q242" s="11"/>
-      <c r="R242" s="11"/>
-      <c r="S242" s="11"/>
-      <c r="T242" s="11"/>
+      <c r="J242" s="10"/>
+      <c r="Q242" s="10"/>
+      <c r="R242" s="10"/>
+      <c r="S242" s="10"/>
+      <c r="T242" s="10"/>
     </row>
     <row r="243">
-      <c r="J243" s="11"/>
-      <c r="Q243" s="11"/>
-      <c r="R243" s="11"/>
-      <c r="S243" s="11"/>
-      <c r="T243" s="11"/>
+      <c r="J243" s="10"/>
+      <c r="Q243" s="10"/>
+      <c r="R243" s="10"/>
+      <c r="S243" s="10"/>
+      <c r="T243" s="10"/>
     </row>
     <row r="244">
-      <c r="J244" s="11"/>
-      <c r="Q244" s="11"/>
-      <c r="R244" s="11"/>
-      <c r="S244" s="11"/>
-      <c r="T244" s="11"/>
+      <c r="J244" s="10"/>
+      <c r="Q244" s="10"/>
+      <c r="R244" s="10"/>
+      <c r="S244" s="10"/>
+      <c r="T244" s="10"/>
     </row>
     <row r="245">
-      <c r="J245" s="11"/>
-      <c r="Q245" s="11"/>
-      <c r="R245" s="11"/>
-      <c r="S245" s="11"/>
-      <c r="T245" s="11"/>
+      <c r="J245" s="10"/>
+      <c r="Q245" s="10"/>
+      <c r="R245" s="10"/>
+      <c r="S245" s="10"/>
+      <c r="T245" s="10"/>
     </row>
     <row r="246">
-      <c r="J246" s="11"/>
-      <c r="Q246" s="11"/>
-      <c r="R246" s="11"/>
-      <c r="S246" s="11"/>
-      <c r="T246" s="11"/>
+      <c r="J246" s="10"/>
+      <c r="Q246" s="10"/>
+      <c r="R246" s="10"/>
+      <c r="S246" s="10"/>
+      <c r="T246" s="10"/>
     </row>
     <row r="247">
-      <c r="J247" s="11"/>
-      <c r="Q247" s="11"/>
-      <c r="R247" s="11"/>
-      <c r="S247" s="11"/>
-      <c r="T247" s="11"/>
+      <c r="J247" s="10"/>
+      <c r="Q247" s="10"/>
+      <c r="R247" s="10"/>
+      <c r="S247" s="10"/>
+      <c r="T247" s="10"/>
     </row>
     <row r="248">
-      <c r="J248" s="11"/>
-      <c r="Q248" s="11"/>
-      <c r="R248" s="11"/>
-      <c r="S248" s="11"/>
-      <c r="T248" s="11"/>
+      <c r="J248" s="10"/>
+      <c r="Q248" s="10"/>
+      <c r="R248" s="10"/>
+      <c r="S248" s="10"/>
+      <c r="T248" s="10"/>
     </row>
     <row r="249">
-      <c r="J249" s="11"/>
-      <c r="Q249" s="11"/>
-      <c r="R249" s="11"/>
-      <c r="S249" s="11"/>
-      <c r="T249" s="11"/>
+      <c r="J249" s="10"/>
+      <c r="Q249" s="10"/>
+      <c r="R249" s="10"/>
+      <c r="S249" s="10"/>
+      <c r="T249" s="10"/>
     </row>
     <row r="250">
-      <c r="J250" s="11"/>
-      <c r="Q250" s="11"/>
-      <c r="R250" s="11"/>
-      <c r="S250" s="11"/>
-      <c r="T250" s="11"/>
+      <c r="J250" s="10"/>
+      <c r="Q250" s="10"/>
+      <c r="R250" s="10"/>
+      <c r="S250" s="10"/>
+      <c r="T250" s="10"/>
     </row>
     <row r="251">
-      <c r="J251" s="11"/>
-      <c r="Q251" s="11"/>
-      <c r="R251" s="11"/>
-      <c r="S251" s="11"/>
-      <c r="T251" s="11"/>
+      <c r="J251" s="10"/>
+      <c r="Q251" s="10"/>
+      <c r="R251" s="10"/>
+      <c r="S251" s="10"/>
+      <c r="T251" s="10"/>
     </row>
     <row r="252">
-      <c r="J252" s="11"/>
-      <c r="Q252" s="11"/>
-      <c r="R252" s="11"/>
-      <c r="S252" s="11"/>
-      <c r="T252" s="11"/>
+      <c r="J252" s="10"/>
+      <c r="Q252" s="10"/>
+      <c r="R252" s="10"/>
+      <c r="S252" s="10"/>
+      <c r="T252" s="10"/>
     </row>
     <row r="253">
-      <c r="J253" s="11"/>
-      <c r="Q253" s="11"/>
-      <c r="R253" s="11"/>
-      <c r="S253" s="11"/>
-      <c r="T253" s="11"/>
+      <c r="J253" s="10"/>
+      <c r="Q253" s="10"/>
+      <c r="R253" s="10"/>
+      <c r="S253" s="10"/>
+      <c r="T253" s="10"/>
     </row>
     <row r="254">
-      <c r="J254" s="11"/>
-      <c r="Q254" s="11"/>
-      <c r="R254" s="11"/>
-      <c r="S254" s="11"/>
-      <c r="T254" s="11"/>
+      <c r="J254" s="10"/>
+      <c r="Q254" s="10"/>
+      <c r="R254" s="10"/>
+      <c r="S254" s="10"/>
+      <c r="T254" s="10"/>
     </row>
     <row r="255">
-      <c r="J255" s="11"/>
-      <c r="Q255" s="11"/>
-      <c r="R255" s="11"/>
-      <c r="S255" s="11"/>
-      <c r="T255" s="11"/>
+      <c r="J255" s="10"/>
+      <c r="Q255" s="10"/>
+      <c r="R255" s="10"/>
+      <c r="S255" s="10"/>
+      <c r="T255" s="10"/>
     </row>
     <row r="256">
-      <c r="J256" s="11"/>
-      <c r="Q256" s="11"/>
-      <c r="R256" s="11"/>
-      <c r="S256" s="11"/>
-      <c r="T256" s="11"/>
+      <c r="J256" s="10"/>
+      <c r="Q256" s="10"/>
+      <c r="R256" s="10"/>
+      <c r="S256" s="10"/>
+      <c r="T256" s="10"/>
     </row>
     <row r="257">
-      <c r="J257" s="11"/>
-      <c r="Q257" s="11"/>
-      <c r="R257" s="11"/>
-      <c r="S257" s="11"/>
-      <c r="T257" s="11"/>
+      <c r="J257" s="10"/>
+      <c r="Q257" s="10"/>
+      <c r="R257" s="10"/>
+      <c r="S257" s="10"/>
+      <c r="T257" s="10"/>
     </row>
     <row r="258">
-      <c r="J258" s="11"/>
-      <c r="Q258" s="11"/>
-      <c r="R258" s="11"/>
-      <c r="S258" s="11"/>
-      <c r="T258" s="11"/>
+      <c r="J258" s="10"/>
+      <c r="Q258" s="10"/>
+      <c r="R258" s="10"/>
+      <c r="S258" s="10"/>
+      <c r="T258" s="10"/>
     </row>
     <row r="259">
-      <c r="J259" s="11"/>
-      <c r="Q259" s="11"/>
-      <c r="R259" s="11"/>
-      <c r="S259" s="11"/>
-      <c r="T259" s="11"/>
+      <c r="J259" s="10"/>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="10"/>
+      <c r="S259" s="10"/>
+      <c r="T259" s="10"/>
     </row>
     <row r="260">
-      <c r="J260" s="11"/>
-      <c r="Q260" s="11"/>
-      <c r="R260" s="11"/>
-      <c r="S260" s="11"/>
-      <c r="T260" s="11"/>
+      <c r="J260" s="10"/>
+      <c r="Q260" s="10"/>
+      <c r="R260" s="10"/>
+      <c r="S260" s="10"/>
+      <c r="T260" s="10"/>
     </row>
     <row r="261">
-      <c r="J261" s="11"/>
-      <c r="Q261" s="11"/>
-      <c r="R261" s="11"/>
-      <c r="S261" s="11"/>
-      <c r="T261" s="11"/>
+      <c r="J261" s="10"/>
+      <c r="Q261" s="10"/>
+      <c r="R261" s="10"/>
+      <c r="S261" s="10"/>
+      <c r="T261" s="10"/>
     </row>
     <row r="262">
-      <c r="J262" s="11"/>
-      <c r="Q262" s="11"/>
-      <c r="R262" s="11"/>
-      <c r="S262" s="11"/>
-      <c r="T262" s="11"/>
+      <c r="J262" s="10"/>
+      <c r="Q262" s="10"/>
+      <c r="R262" s="10"/>
+      <c r="S262" s="10"/>
+      <c r="T262" s="10"/>
     </row>
     <row r="263">
-      <c r="J263" s="11"/>
-      <c r="Q263" s="11"/>
-      <c r="R263" s="11"/>
-      <c r="S263" s="11"/>
-      <c r="T263" s="11"/>
+      <c r="J263" s="10"/>
+      <c r="Q263" s="10"/>
+      <c r="R263" s="10"/>
+      <c r="S263" s="10"/>
+      <c r="T263" s="10"/>
     </row>
     <row r="264">
-      <c r="J264" s="11"/>
-      <c r="Q264" s="11"/>
-      <c r="R264" s="11"/>
-      <c r="S264" s="11"/>
-      <c r="T264" s="11"/>
+      <c r="J264" s="10"/>
+      <c r="Q264" s="10"/>
+      <c r="R264" s="10"/>
+      <c r="S264" s="10"/>
+      <c r="T264" s="10"/>
     </row>
     <row r="265">
-      <c r="J265" s="11"/>
-      <c r="Q265" s="11"/>
-      <c r="R265" s="11"/>
-      <c r="S265" s="11"/>
-      <c r="T265" s="11"/>
+      <c r="J265" s="10"/>
+      <c r="Q265" s="10"/>
+      <c r="R265" s="10"/>
+      <c r="S265" s="10"/>
+      <c r="T265" s="10"/>
     </row>
     <row r="266">
-      <c r="J266" s="11"/>
-      <c r="Q266" s="11"/>
-      <c r="R266" s="11"/>
-      <c r="S266" s="11"/>
-      <c r="T266" s="11"/>
+      <c r="J266" s="10"/>
+      <c r="Q266" s="10"/>
+      <c r="R266" s="10"/>
+      <c r="S266" s="10"/>
+      <c r="T266" s="10"/>
     </row>
     <row r="267">
-      <c r="J267" s="11"/>
-      <c r="Q267" s="11"/>
-      <c r="R267" s="11"/>
-      <c r="S267" s="11"/>
-      <c r="T267" s="11"/>
+      <c r="J267" s="10"/>
+      <c r="Q267" s="10"/>
+      <c r="R267" s="10"/>
+      <c r="S267" s="10"/>
+      <c r="T267" s="10"/>
     </row>
     <row r="268">
-      <c r="J268" s="11"/>
-      <c r="Q268" s="11"/>
-      <c r="R268" s="11"/>
-      <c r="S268" s="11"/>
-      <c r="T268" s="11"/>
+      <c r="J268" s="10"/>
+      <c r="Q268" s="10"/>
+      <c r="R268" s="10"/>
+      <c r="S268" s="10"/>
+      <c r="T268" s="10"/>
     </row>
     <row r="269">
-      <c r="J269" s="11"/>
-      <c r="Q269" s="11"/>
-      <c r="R269" s="11"/>
-      <c r="S269" s="11"/>
-      <c r="T269" s="11"/>
+      <c r="J269" s="10"/>
+      <c r="Q269" s="10"/>
+      <c r="R269" s="10"/>
+      <c r="S269" s="10"/>
+      <c r="T269" s="10"/>
     </row>
     <row r="270">
-      <c r="J270" s="11"/>
-      <c r="Q270" s="11"/>
-      <c r="R270" s="11"/>
-      <c r="S270" s="11"/>
-      <c r="T270" s="11"/>
+      <c r="J270" s="10"/>
+      <c r="Q270" s="10"/>
+      <c r="R270" s="10"/>
+      <c r="S270" s="10"/>
+      <c r="T270" s="10"/>
     </row>
     <row r="271">
-      <c r="J271" s="11"/>
-      <c r="Q271" s="11"/>
-      <c r="R271" s="11"/>
-      <c r="S271" s="11"/>
-      <c r="T271" s="11"/>
+      <c r="J271" s="10"/>
+      <c r="Q271" s="10"/>
+      <c r="R271" s="10"/>
+      <c r="S271" s="10"/>
+      <c r="T271" s="10"/>
     </row>
     <row r="272">
-      <c r="J272" s="11"/>
-      <c r="Q272" s="11"/>
-      <c r="R272" s="11"/>
-      <c r="S272" s="11"/>
-      <c r="T272" s="11"/>
+      <c r="J272" s="10"/>
+      <c r="Q272" s="10"/>
+      <c r="R272" s="10"/>
+      <c r="S272" s="10"/>
+      <c r="T272" s="10"/>
     </row>
     <row r="273">
-      <c r="J273" s="11"/>
-      <c r="Q273" s="11"/>
-      <c r="R273" s="11"/>
-      <c r="S273" s="11"/>
-      <c r="T273" s="11"/>
+      <c r="J273" s="10"/>
+      <c r="Q273" s="10"/>
+      <c r="R273" s="10"/>
+      <c r="S273" s="10"/>
+      <c r="T273" s="10"/>
     </row>
     <row r="274">
-      <c r="J274" s="11"/>
-      <c r="Q274" s="11"/>
-      <c r="R274" s="11"/>
-      <c r="S274" s="11"/>
-      <c r="T274" s="11"/>
+      <c r="J274" s="10"/>
+      <c r="Q274" s="10"/>
+      <c r="R274" s="10"/>
+      <c r="S274" s="10"/>
+      <c r="T274" s="10"/>
     </row>
     <row r="275">
-      <c r="J275" s="11"/>
-      <c r="Q275" s="11"/>
-      <c r="R275" s="11"/>
-      <c r="S275" s="11"/>
-      <c r="T275" s="11"/>
+      <c r="J275" s="10"/>
+      <c r="Q275" s="10"/>
+      <c r="R275" s="10"/>
+      <c r="S275" s="10"/>
+      <c r="T275" s="10"/>
     </row>
     <row r="276">
-      <c r="J276" s="11"/>
-      <c r="Q276" s="11"/>
-      <c r="R276" s="11"/>
-      <c r="S276" s="11"/>
-      <c r="T276" s="11"/>
+      <c r="J276" s="10"/>
+      <c r="Q276" s="10"/>
+      <c r="R276" s="10"/>
+      <c r="S276" s="10"/>
+      <c r="T276" s="10"/>
     </row>
     <row r="277">
-      <c r="J277" s="11"/>
-      <c r="Q277" s="11"/>
-      <c r="R277" s="11"/>
-      <c r="S277" s="11"/>
-      <c r="T277" s="11"/>
+      <c r="J277" s="10"/>
+      <c r="Q277" s="10"/>
+      <c r="R277" s="10"/>
+      <c r="S277" s="10"/>
+      <c r="T277" s="10"/>
     </row>
     <row r="278">
-      <c r="J278" s="11"/>
-      <c r="Q278" s="11"/>
-      <c r="R278" s="11"/>
-      <c r="S278" s="11"/>
-      <c r="T278" s="11"/>
+      <c r="J278" s="10"/>
+      <c r="Q278" s="10"/>
+      <c r="R278" s="10"/>
+      <c r="S278" s="10"/>
+      <c r="T278" s="10"/>
     </row>
     <row r="279">
-      <c r="J279" s="11"/>
-      <c r="Q279" s="11"/>
-      <c r="R279" s="11"/>
-      <c r="S279" s="11"/>
-      <c r="T279" s="11"/>
+      <c r="J279" s="10"/>
+      <c r="Q279" s="10"/>
+      <c r="R279" s="10"/>
+      <c r="S279" s="10"/>
+      <c r="T279" s="10"/>
     </row>
     <row r="280">
-      <c r="J280" s="11"/>
-      <c r="Q280" s="11"/>
-      <c r="R280" s="11"/>
-      <c r="S280" s="11"/>
-      <c r="T280" s="11"/>
+      <c r="J280" s="10"/>
+      <c r="Q280" s="10"/>
+      <c r="R280" s="10"/>
+      <c r="S280" s="10"/>
+      <c r="T280" s="10"/>
     </row>
     <row r="281">
-      <c r="J281" s="11"/>
-      <c r="Q281" s="11"/>
-      <c r="R281" s="11"/>
-      <c r="S281" s="11"/>
-      <c r="T281" s="11"/>
+      <c r="J281" s="10"/>
+      <c r="Q281" s="10"/>
+      <c r="R281" s="10"/>
+      <c r="S281" s="10"/>
+      <c r="T281" s="10"/>
     </row>
     <row r="282">
-      <c r="J282" s="11"/>
-      <c r="Q282" s="11"/>
-      <c r="R282" s="11"/>
-      <c r="S282" s="11"/>
-      <c r="T282" s="11"/>
+      <c r="J282" s="10"/>
+      <c r="Q282" s="10"/>
+      <c r="R282" s="10"/>
+      <c r="S282" s="10"/>
+      <c r="T282" s="10"/>
     </row>
     <row r="283">
-      <c r="J283" s="11"/>
-      <c r="Q283" s="11"/>
-      <c r="R283" s="11"/>
-      <c r="S283" s="11"/>
-      <c r="T283" s="11"/>
+      <c r="J283" s="10"/>
+      <c r="Q283" s="10"/>
+      <c r="R283" s="10"/>
+      <c r="S283" s="10"/>
+      <c r="T283" s="10"/>
     </row>
     <row r="284">
-      <c r="J284" s="11"/>
-      <c r="Q284" s="11"/>
-      <c r="R284" s="11"/>
-      <c r="S284" s="11"/>
-      <c r="T284" s="11"/>
+      <c r="J284" s="10"/>
+      <c r="Q284" s="10"/>
+      <c r="R284" s="10"/>
+      <c r="S284" s="10"/>
+      <c r="T284" s="10"/>
     </row>
     <row r="285">
-      <c r="J285" s="11"/>
-      <c r="Q285" s="11"/>
-      <c r="R285" s="11"/>
-      <c r="S285" s="11"/>
-      <c r="T285" s="11"/>
+      <c r="J285" s="10"/>
+      <c r="Q285" s="10"/>
+      <c r="R285" s="10"/>
+      <c r="S285" s="10"/>
+      <c r="T285" s="10"/>
     </row>
     <row r="286">
-      <c r="J286" s="11"/>
-      <c r="Q286" s="11"/>
-      <c r="R286" s="11"/>
-      <c r="S286" s="11"/>
-      <c r="T286" s="11"/>
+      <c r="J286" s="10"/>
+      <c r="Q286" s="10"/>
+      <c r="R286" s="10"/>
+      <c r="S286" s="10"/>
+      <c r="T286" s="10"/>
     </row>
     <row r="287">
-      <c r="J287" s="11"/>
-      <c r="Q287" s="11"/>
-      <c r="R287" s="11"/>
-      <c r="S287" s="11"/>
-      <c r="T287" s="11"/>
+      <c r="J287" s="10"/>
+      <c r="Q287" s="10"/>
+      <c r="R287" s="10"/>
+      <c r="S287" s="10"/>
+      <c r="T287" s="10"/>
     </row>
     <row r="288">
-      <c r="J288" s="11"/>
-      <c r="Q288" s="11"/>
-      <c r="R288" s="11"/>
-      <c r="S288" s="11"/>
-      <c r="T288" s="11"/>
+      <c r="J288" s="10"/>
+      <c r="Q288" s="10"/>
+      <c r="R288" s="10"/>
+      <c r="S288" s="10"/>
+      <c r="T288" s="10"/>
     </row>
     <row r="289">
-      <c r="J289" s="11"/>
-      <c r="Q289" s="11"/>
-      <c r="R289" s="11"/>
-      <c r="S289" s="11"/>
-      <c r="T289" s="11"/>
+      <c r="J289" s="10"/>
+      <c r="Q289" s="10"/>
+      <c r="R289" s="10"/>
+      <c r="S289" s="10"/>
+      <c r="T289" s="10"/>
     </row>
     <row r="290">
-      <c r="J290" s="11"/>
-      <c r="Q290" s="11"/>
-      <c r="R290" s="11"/>
-      <c r="S290" s="11"/>
-      <c r="T290" s="11"/>
+      <c r="J290" s="10"/>
+      <c r="Q290" s="10"/>
+      <c r="R290" s="10"/>
+      <c r="S290" s="10"/>
+      <c r="T290" s="10"/>
     </row>
     <row r="291">
-      <c r="J291" s="11"/>
-      <c r="Q291" s="11"/>
-      <c r="R291" s="11"/>
-      <c r="S291" s="11"/>
-      <c r="T291" s="11"/>
+      <c r="J291" s="10"/>
+      <c r="Q291" s="10"/>
+      <c r="R291" s="10"/>
+      <c r="S291" s="10"/>
+      <c r="T291" s="10"/>
     </row>
     <row r="292">
-      <c r="J292" s="11"/>
-      <c r="Q292" s="11"/>
-      <c r="R292" s="11"/>
-      <c r="S292" s="11"/>
-      <c r="T292" s="11"/>
+      <c r="J292" s="10"/>
+      <c r="Q292" s="10"/>
+      <c r="R292" s="10"/>
+      <c r="S292" s="10"/>
+      <c r="T292" s="10"/>
     </row>
     <row r="293">
-      <c r="J293" s="11"/>
-      <c r="Q293" s="11"/>
-      <c r="R293" s="11"/>
-      <c r="S293" s="11"/>
-      <c r="T293" s="11"/>
+      <c r="J293" s="10"/>
+      <c r="Q293" s="10"/>
+      <c r="R293" s="10"/>
+      <c r="S293" s="10"/>
+      <c r="T293" s="10"/>
     </row>
     <row r="294">
-      <c r="J294" s="11"/>
-      <c r="Q294" s="11"/>
-      <c r="R294" s="11"/>
-      <c r="S294" s="11"/>
-      <c r="T294" s="11"/>
+      <c r="J294" s="10"/>
+      <c r="Q294" s="10"/>
+      <c r="R294" s="10"/>
+      <c r="S294" s="10"/>
+      <c r="T294" s="10"/>
     </row>
     <row r="295">
-      <c r="J295" s="11"/>
-      <c r="Q295" s="11"/>
-      <c r="R295" s="11"/>
-      <c r="S295" s="11"/>
-      <c r="T295" s="11"/>
+      <c r="J295" s="10"/>
+      <c r="Q295" s="10"/>
+      <c r="R295" s="10"/>
+      <c r="S295" s="10"/>
+      <c r="T295" s="10"/>
     </row>
     <row r="296">
-      <c r="J296" s="11"/>
-      <c r="Q296" s="11"/>
-      <c r="R296" s="11"/>
-      <c r="S296" s="11"/>
-      <c r="T296" s="11"/>
+      <c r="J296" s="10"/>
+      <c r="Q296" s="10"/>
+      <c r="R296" s="10"/>
+      <c r="S296" s="10"/>
+      <c r="T296" s="10"/>
     </row>
     <row r="297">
-      <c r="J297" s="11"/>
-      <c r="Q297" s="11"/>
-      <c r="R297" s="11"/>
-      <c r="S297" s="11"/>
-      <c r="T297" s="11"/>
+      <c r="J297" s="10"/>
+      <c r="Q297" s="10"/>
+      <c r="R297" s="10"/>
+      <c r="S297" s="10"/>
+      <c r="T297" s="10"/>
     </row>
     <row r="298">
-      <c r="J298" s="11"/>
-      <c r="Q298" s="11"/>
-      <c r="R298" s="11"/>
-      <c r="S298" s="11"/>
-      <c r="T298" s="11"/>
+      <c r="J298" s="10"/>
+      <c r="Q298" s="10"/>
+      <c r="R298" s="10"/>
+      <c r="S298" s="10"/>
+      <c r="T298" s="10"/>
     </row>
     <row r="299">
-      <c r="J299" s="11"/>
-      <c r="Q299" s="11"/>
-      <c r="R299" s="11"/>
-      <c r="S299" s="11"/>
-      <c r="T299" s="11"/>
+      <c r="J299" s="10"/>
+      <c r="Q299" s="10"/>
+      <c r="R299" s="10"/>
+      <c r="S299" s="10"/>
+      <c r="T299" s="10"/>
     </row>
     <row r="300">
-      <c r="J300" s="11"/>
-      <c r="Q300" s="11"/>
-      <c r="R300" s="11"/>
-      <c r="S300" s="11"/>
-      <c r="T300" s="11"/>
+      <c r="J300" s="10"/>
+      <c r="Q300" s="10"/>
+      <c r="R300" s="10"/>
+      <c r="S300" s="10"/>
+      <c r="T300" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$4:$V$19"/>
@@ -6009,6 +6010,9 @@
       <formula1>"NOT ACCEPTED,ACCEPTED,ACCEPTED WITH CONDITIONS,REJECTED,DEFERRED"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6027,149 +6031,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <f>COUNTA('Master Register'!A5:A300)</f>
         <v>29</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>120</v>
+      <c r="C3" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="10">
         <f>COUNTIF('Master Register'!D5:D300,"P0")</f>
         <v>16</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>164</v>
+      <c r="C4" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="11">
+      <c r="A5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="10">
         <f>COUNTIF('Master Register'!D5:D300,"P1")</f>
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>190</v>
+      <c r="C5" s="5" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="10">
         <f>COUNTIF('Master Register'!Q5:Q300,"OPEN")</f>
         <v>29</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>208</v>
+      <c r="C6" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="10">
         <f>COUNTIF('Master Register'!Q5:Q300,"IN_PROGRESS")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>230</v>
+      <c r="C7" s="5" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="10">
         <f>COUNTIF('Master Register'!Q5:Q300,"EVIDENCE_SUBMITTED")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>247</v>
+      <c r="C8" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="10">
         <f>COUNTIF('Master Register'!T5:T300,"ACCEPTED")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>267</v>
+      <c r="C9" s="5" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="10">
         <f>COUNTIF('Master Register'!T5:T300,"REJECTED")</f>
         <v>0</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>277</v>
+      <c r="C10" s="5" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>279</v>
+      <c r="A11" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="B11" s="13">
         <f>IF(B3=0,0,B9/B3)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>303</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="11" t="str">
+      <c r="A14" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="10" t="str">
         <f>IF(AND(B4=COUNTIFS('Master Register'!D5:D300,"P0",'Master Register'!T5:T300,"ACCEPTED"),COUNTIF('Master Register'!T5:T300,"REJECTED")=0),"P0 CLEAR","BLOCKED")</f>
         <v>BLOCKED</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>341</v>
+      <c r="C14" s="5" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -6198,772 +6202,772 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="C3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>97</v>
+      <c r="D4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="A5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>97</v>
+      <c r="D6" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="D7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>97</v>
+      <c r="F7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>97</v>
+      <c r="D8" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="A9" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>97</v>
+      <c r="G10" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>97</v>
+      <c r="F11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="A12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>97</v>
+      <c r="F12" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21">
-      <c r="G21" s="11"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="22">
-      <c r="G22" s="11"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23">
-      <c r="G23" s="11"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24">
-      <c r="G24" s="11"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25">
-      <c r="G25" s="11"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26">
-      <c r="G26" s="11"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27">
-      <c r="G27" s="11"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28">
-      <c r="G28" s="11"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29">
-      <c r="G29" s="11"/>
+      <c r="G29" s="10"/>
     </row>
     <row r="30">
-      <c r="G30" s="11"/>
+      <c r="G30" s="10"/>
     </row>
     <row r="31">
-      <c r="G31" s="11"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32">
-      <c r="G32" s="11"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33">
-      <c r="G33" s="11"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34">
-      <c r="G34" s="11"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35">
-      <c r="G35" s="11"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="36">
-      <c r="G36" s="11"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37">
-      <c r="G37" s="11"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38">
-      <c r="G38" s="11"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39">
-      <c r="G39" s="11"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40">
-      <c r="G40" s="11"/>
+      <c r="G40" s="10"/>
     </row>
     <row r="41">
-      <c r="G41" s="11"/>
+      <c r="G41" s="10"/>
     </row>
     <row r="42">
-      <c r="G42" s="11"/>
+      <c r="G42" s="10"/>
     </row>
     <row r="43">
-      <c r="G43" s="11"/>
+      <c r="G43" s="10"/>
     </row>
     <row r="44">
-      <c r="G44" s="11"/>
+      <c r="G44" s="10"/>
     </row>
     <row r="45">
-      <c r="G45" s="11"/>
+      <c r="G45" s="10"/>
     </row>
     <row r="46">
-      <c r="G46" s="11"/>
+      <c r="G46" s="10"/>
     </row>
     <row r="47">
-      <c r="G47" s="11"/>
+      <c r="G47" s="10"/>
     </row>
     <row r="48">
-      <c r="G48" s="11"/>
+      <c r="G48" s="10"/>
     </row>
     <row r="49">
-      <c r="G49" s="11"/>
+      <c r="G49" s="10"/>
     </row>
     <row r="50">
-      <c r="G50" s="11"/>
+      <c r="G50" s="10"/>
     </row>
     <row r="51">
-      <c r="G51" s="11"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52">
-      <c r="G52" s="11"/>
+      <c r="G52" s="10"/>
     </row>
     <row r="53">
-      <c r="G53" s="11"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54">
-      <c r="G54" s="11"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55">
-      <c r="G55" s="11"/>
+      <c r="G55" s="10"/>
     </row>
     <row r="56">
-      <c r="G56" s="11"/>
+      <c r="G56" s="10"/>
     </row>
     <row r="57">
-      <c r="G57" s="11"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58">
-      <c r="G58" s="11"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59">
-      <c r="G59" s="11"/>
+      <c r="G59" s="10"/>
     </row>
     <row r="60">
-      <c r="G60" s="11"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61">
-      <c r="G61" s="11"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62">
-      <c r="G62" s="11"/>
+      <c r="G62" s="10"/>
     </row>
     <row r="63">
-      <c r="G63" s="11"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64">
-      <c r="G64" s="11"/>
+      <c r="G64" s="10"/>
     </row>
     <row r="65">
-      <c r="G65" s="11"/>
+      <c r="G65" s="10"/>
     </row>
     <row r="66">
-      <c r="G66" s="11"/>
+      <c r="G66" s="10"/>
     </row>
     <row r="67">
-      <c r="G67" s="11"/>
+      <c r="G67" s="10"/>
     </row>
     <row r="68">
-      <c r="G68" s="11"/>
+      <c r="G68" s="10"/>
     </row>
     <row r="69">
-      <c r="G69" s="11"/>
+      <c r="G69" s="10"/>
     </row>
     <row r="70">
-      <c r="G70" s="11"/>
+      <c r="G70" s="10"/>
     </row>
     <row r="71">
-      <c r="G71" s="11"/>
+      <c r="G71" s="10"/>
     </row>
     <row r="72">
-      <c r="G72" s="11"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73">
-      <c r="G73" s="11"/>
+      <c r="G73" s="10"/>
     </row>
     <row r="74">
-      <c r="G74" s="11"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75">
-      <c r="G75" s="11"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76">
-      <c r="G76" s="11"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77">
-      <c r="G77" s="11"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78">
-      <c r="G78" s="11"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79">
-      <c r="G79" s="11"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80">
-      <c r="G80" s="11"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81">
-      <c r="G81" s="11"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82">
-      <c r="G82" s="11"/>
+      <c r="G82" s="10"/>
     </row>
     <row r="83">
-      <c r="G83" s="11"/>
+      <c r="G83" s="10"/>
     </row>
     <row r="84">
-      <c r="G84" s="11"/>
+      <c r="G84" s="10"/>
     </row>
     <row r="85">
-      <c r="G85" s="11"/>
+      <c r="G85" s="10"/>
     </row>
     <row r="86">
-      <c r="G86" s="11"/>
+      <c r="G86" s="10"/>
     </row>
     <row r="87">
-      <c r="G87" s="11"/>
+      <c r="G87" s="10"/>
     </row>
     <row r="88">
-      <c r="G88" s="11"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89">
-      <c r="G89" s="11"/>
+      <c r="G89" s="10"/>
     </row>
     <row r="90">
-      <c r="G90" s="11"/>
+      <c r="G90" s="10"/>
     </row>
     <row r="91">
-      <c r="G91" s="11"/>
+      <c r="G91" s="10"/>
     </row>
     <row r="92">
-      <c r="G92" s="11"/>
+      <c r="G92" s="10"/>
     </row>
     <row r="93">
-      <c r="G93" s="11"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94">
-      <c r="G94" s="11"/>
+      <c r="G94" s="10"/>
     </row>
     <row r="95">
-      <c r="G95" s="11"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96">
-      <c r="G96" s="11"/>
+      <c r="G96" s="10"/>
     </row>
     <row r="97">
-      <c r="G97" s="11"/>
+      <c r="G97" s="10"/>
     </row>
     <row r="98">
-      <c r="G98" s="11"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99">
-      <c r="G99" s="11"/>
+      <c r="G99" s="10"/>
     </row>
     <row r="100">
-      <c r="G100" s="11"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101">
-      <c r="G101" s="11"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102">
-      <c r="G102" s="11"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103">
-      <c r="G103" s="11"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104">
-      <c r="G104" s="11"/>
+      <c r="G104" s="10"/>
     </row>
     <row r="105">
-      <c r="G105" s="11"/>
+      <c r="G105" s="10"/>
     </row>
     <row r="106">
-      <c r="G106" s="11"/>
+      <c r="G106" s="10"/>
     </row>
     <row r="107">
-      <c r="G107" s="11"/>
+      <c r="G107" s="10"/>
     </row>
     <row r="108">
-      <c r="G108" s="11"/>
+      <c r="G108" s="10"/>
     </row>
     <row r="109">
-      <c r="G109" s="11"/>
+      <c r="G109" s="10"/>
     </row>
     <row r="110">
-      <c r="G110" s="11"/>
+      <c r="G110" s="10"/>
     </row>
     <row r="111">
-      <c r="G111" s="11"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112">
-      <c r="G112" s="11"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113">
-      <c r="G113" s="11"/>
+      <c r="G113" s="10"/>
     </row>
     <row r="114">
-      <c r="G114" s="11"/>
+      <c r="G114" s="10"/>
     </row>
     <row r="115">
-      <c r="G115" s="11"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116">
-      <c r="G116" s="11"/>
+      <c r="G116" s="10"/>
     </row>
     <row r="117">
-      <c r="G117" s="11"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118">
-      <c r="G118" s="11"/>
+      <c r="G118" s="10"/>
     </row>
     <row r="119">
-      <c r="G119" s="11"/>
+      <c r="G119" s="10"/>
     </row>
     <row r="120">
-      <c r="G120" s="11"/>
+      <c r="G120" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6995,235 +6999,235 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="7" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="D4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="C5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="F6" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="B8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="E8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="B9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>94</v>
+      <c r="D9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
@@ -7231,76 +7235,76 @@
         <v>128</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>171</v>
@@ -7328,218 +7332,218 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>292</v>
+      <c r="A1" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>301</v>
+      <c r="A2" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
